--- a/job_api_catalog.xlsx
+++ b/job_api_catalog.xlsx
@@ -8194,7 +8194,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>No Public API</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>No Public API</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>No Public API</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>Enterprise Only</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>Enterprise Only</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>Enterprise Only</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>Enterprise Only</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>Enterprise Only</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>No Public API</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Not Recommended</t>
+          <t>No Public API</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Whether this (API, Region) row is Integrated (live in jobs.py today), Recommended (researched, not yet integrated, report recommends adding), or Not Recommended (researched and explicitly ruled out - e.g. no public API, partner-only, or per-tenant-only).</t>
+          <t>Whether this (API, Region) row is Integrated (live in jobs.py today), Recommended (researched, not yet integrated, report recommends adding), Not Recommended (researched and the report explicitly advises against pursuing it - e.g. scraping-only with a stated legal/maintenance caution), No Public API (no official or workable public endpoint exists at all), or Enterprise Only (an API exists but only via a paid/partner/per-tenant enterprise agreement, not a public aggregatable feed).</t>
         </is>
       </c>
     </row>

--- a/job_api_catalog.xlsx
+++ b/job_api_catalog.xlsx
@@ -62,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -73,6 +73,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -13934,9 +13937,9 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R105" s="8" t="inlineStr">
+        <is>
+          <t>10,000-20,000 (if partner approval granted; report Sec 12 item 5)</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -13947,6 +13950,46 @@
       <c r="T105" t="inlineStr">
         <is>
           <t>Investigate/Add if partner approval granted (Medium effort)</t>
+        </is>
+      </c>
+      <c r="U105" s="8" t="inlineStr">
+        <is>
+          <t>United States (non-federal, National Labor Exchange aggregation)</t>
+        </is>
+      </c>
+      <c r="V105" s="8" t="inlineStr">
+        <is>
+          <t>N/A - US-only by design (a national labor-exchange service)</t>
+        </is>
+      </c>
+      <c r="W105" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; access requires NLx Research Hub Governance Board partner approval and a registered token before any code can be written.</t>
+        </is>
+      </c>
+      <c r="X105" s="8" t="inlineStr">
+        <is>
+          <t>New API integration once partner approval is granted: register for a token, implement pagination + keyword/occupation(O*NET)/location filters, and add as a new sources/ module following the existing pattern.</t>
+        </is>
+      </c>
+      <c r="Y105" s="8" t="inlineStr">
+        <is>
+          <t>+10,000-20,000 (if approved; report Sec 12 item 5)</t>
+        </is>
+      </c>
+      <c r="Z105" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA105" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB105" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (blocked on partner/governance approval, not on engineering complexity)</t>
         </is>
       </c>
     </row>
@@ -14034,9 +14077,9 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R106" s="8" t="inlineStr">
+        <is>
+          <t>Budget-dependent, potentially 50,000+ (3M+/mo global index at ~$1/1,000 jobs; report Sec 12 item 7)</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -14047,6 +14090,46 @@
       <c r="T106" t="inlineStr">
         <is>
           <t>Add if budget allows (Low effort, paid)</t>
+        </is>
+      </c>
+      <c r="U106" s="8" t="inlineStr">
+        <is>
+          <t>Global, ATS-sourced (Workday, Greenhouse, Lever, BambooHR, SuccessFactors, Oracle, 54 platforms, 200k+ career sites), heavily US/English-speaking</t>
+        </is>
+      </c>
+      <c r="V106" s="8" t="inlineStr">
+        <is>
+          <t>Already global including India, Europe, LATAM, SEA per its own index - a single integration would add breadth across every target region at once</t>
+        </is>
+      </c>
+      <c r="W106" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; requires a paid RapidAPI subscription (free trial only) before any jobs can be pulled.</t>
+        </is>
+      </c>
+      <c r="X106" s="8" t="inlineStr">
+        <is>
+          <t>New API integration: register on RapidAPI, implement pagination/date/location/remote filters, and cap pull volume to match budget once a paid plan is approved.</t>
+        </is>
+      </c>
+      <c r="Y106" s="8" t="inlineStr">
+        <is>
+          <t>+50,000+ (budget-bound; report Sec 12 item 7)</t>
+        </is>
+      </c>
+      <c r="Z106" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA106" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB106" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (straightforward REST + key; effort is Low, the constraint is budget approval, not engineering)</t>
         </is>
       </c>
     </row>
@@ -14134,9 +14217,9 @@
       <c r="Q107" t="n">
         <v>0</v>
       </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R107" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (enterprise scale play; realistic pull is entirely a function of the purchased plan/quota, not the API's own ceiling)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -14147,6 +14230,46 @@
       <c r="T107" t="inlineStr">
         <is>
           <t>Enterprise-only scale play, cost-gated (Medium effort)</t>
+        </is>
+      </c>
+      <c r="U107" s="8" t="inlineStr">
+        <is>
+          <t>Global multi-source dataset (399M+ records), incl. United States</t>
+        </is>
+      </c>
+      <c r="V107" s="8" t="inlineStr">
+        <is>
+          <t>Already global including India and other target regions - one integration covers all</t>
+        </is>
+      </c>
+      <c r="W107" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; enterprise-only paid plan (from $49/mo) with no free tier to prototype against.</t>
+        </is>
+      </c>
+      <c r="X107" s="8" t="inlineStr">
+        <is>
+          <t>New API integration, but realistically an enterprise/procurement decision first (get a paid plan) before any engineering starts.</t>
+        </is>
+      </c>
+      <c r="Y107" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (budget-dependent enterprise plan)</t>
+        </is>
+      </c>
+      <c r="Z107" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA107" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB107" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (procurement + New API integration)</t>
         </is>
       </c>
     </row>
@@ -14234,9 +14357,9 @@
       <c r="Q108" t="n">
         <v>0</v>
       </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R108" s="8" t="inlineStr">
+        <is>
+          <t>20,000-50,000 (bulk monthly dataset; report Sec 12 item 10, combined estimate shared with NCS India)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -14247,6 +14370,46 @@
       <c r="T108" t="inlineStr">
         <is>
           <t>Add - Critical priority for Canada (Medium-High effort, partner approval)</t>
+        </is>
+      </c>
+      <c r="U108" s="8" t="inlineStr">
+        <is>
+          <t>Canada (national public job board)</t>
+        </is>
+      </c>
+      <c r="V108" s="8" t="inlineStr">
+        <is>
+          <t>N/A - Canada-only by design (a national government service)</t>
+        </is>
+      </c>
+      <c r="W108" s="8" t="inlineStr">
+        <is>
+          <t>The live XML feed requires a partner-access agreement with ESDC; the freely-downloadable Open Government dataset exists but refreshes only monthly (poor freshness) and needs its own bulk-ETL ingestion path, neither of which exist in this project today.</t>
+        </is>
+      </c>
+      <c r="X108" s="8" t="inlineStr">
+        <is>
+          <t>Two paths: (1) request partner feed access for near-real-time data (Medium-High effort, approval-gated), or (2) build a monthly bulk-ETL job against the Open Government Portal dataset (no approval needed, but a new ingestion pattern this project doesn't currently have, since every existing source is a live API pull).</t>
+        </is>
+      </c>
+      <c r="Y108" s="8" t="inlineStr">
+        <is>
+          <t>+20,000-50,000 combined with NCS India (report Sec 12 item 10); Canada-only share not separately broken out</t>
+        </is>
+      </c>
+      <c r="Z108" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA108" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB108" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (partner feed) or Custom connector (monthly bulk-dataset ETL, a new ingestion pattern for this project)</t>
         </is>
       </c>
     </row>
@@ -14334,9 +14497,9 @@
       <c r="Q109" t="n">
         <v>2001</v>
       </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>22,000-42,000</t>
+      <c r="R109" s="8" t="inlineStr">
+        <is>
+          <t>22,000-42,000 (same self-capped ceiling as the existing Adzuna integration, shared across all countries queried)</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -14347,6 +14510,46 @@
       <c r="T109" t="inlineStr">
         <is>
           <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="U109" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried by this project; Adzuna's own Canadian index is a broad private-sector national feed</t>
+        </is>
+      </c>
+      <c r="V109" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional region for the already-integrated Adzuna provider (see the Integrated Adzuna rows' 'Additional Supported Regions' column) - Canada is reachable today with the existing app_id/app_key, simply unqueried</t>
+        </is>
+      </c>
+      <c r="W109" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - the same key already used for the US query covers Canada. The only 'gap' is that sources/adzuna.py hardcodes COUNTRY = "us" instead of looping over multiple countries.</t>
+        </is>
+      </c>
+      <c r="X109" s="8" t="inlineStr">
+        <is>
+          <t>Configuration/small code change: add "ca" to a COUNTRIES list in sources/adzuna.py alongside "us" - no new credentials, no new integration.</t>
+        </is>
+      </c>
+      <c r="Y109" s="8" t="inlineStr">
+        <is>
+          <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="Z109" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA109" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB109" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated Adzuna row's fix: replace COUNTRY = "us" with a loop over a COUNTRIES list in sources/adzuna.py</t>
         </is>
       </c>
     </row>
@@ -14434,9 +14637,9 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R110" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (potentially large per research, but the read-access model for third parties is unconfirmed - could be zero if no consumer feed exists at all)</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -14447,6 +14650,46 @@
       <c r="T110" t="inlineStr">
         <is>
           <t>Investigate - confirm read-access model first (Unknown effort)</t>
+        </is>
+      </c>
+      <c r="U110" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom (successor to Universal Jobmatch)</t>
+        </is>
+      </c>
+      <c r="V110" s="8" t="inlineStr">
+        <is>
+          <t>N/A - UK-only government service</t>
+        </is>
+      </c>
+      <c r="W110" s="8" t="inlineStr">
+        <is>
+          <t>Whether a third-party consumer read API even exists is unconfirmed - only a bulk-upload spec for employers posting jobs is documented; this needs to be verified before any integration can be scoped.</t>
+        </is>
+      </c>
+      <c r="X110" s="8" t="inlineStr">
+        <is>
+          <t>Investigate first: confirm whether a consumer-read feed exists at all (contact DWP / check the API Catalogue). If one exists, this becomes a New API integration; if not, this candidate should be dropped.</t>
+        </is>
+      </c>
+      <c r="Y110" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (access model unconfirmed)</t>
+        </is>
+      </c>
+      <c r="Z110" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA110" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB110" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (pending confirmation that a consumer-read feed actually exists)</t>
         </is>
       </c>
     </row>
@@ -14536,9 +14779,9 @@
           <t>Unknown - folds into the combined 1,125-job SerpApi+OpenWeb Ninja+Careerjet total; not separable (see Notes)</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>7,000-12,000</t>
+      <c r="R111" s="8" t="inlineStr">
+        <is>
+          <t>7,000-12,000 (same self-capped ceiling as the existing Careerjet integration, shared across all locales queried)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -14549,6 +14792,46 @@
       <c r="T111" t="inlineStr">
         <is>
           <t>+5,000-10,000 by adding locale/country-scoped passes plus real keyword searches (Low difficulty)</t>
+        </is>
+      </c>
+      <c r="U111" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried with a UK-scoped pass; the already-integrated Careerjet key covers this via locale_code</t>
+        </is>
+      </c>
+      <c r="V111" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-locale opportunity for the already-integrated Careerjet provider - UK is reachable today via the unused locale_code param</t>
+        </is>
+      </c>
+      <c r="W111" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - Careerjet is already integrated and the key already works; the current implementation just runs one wildcard, implicitly-US-biased query instead of locale-scoped passes.</t>
+        </is>
+      </c>
+      <c r="X111" s="8" t="inlineStr">
+        <is>
+          <t>Small code change: add a UK-scoped pass (locale_code="uk") with real keywords alongside the existing wildcard query in sources/careerjet.py.</t>
+        </is>
+      </c>
+      <c r="Y111" s="8" t="inlineStr">
+        <is>
+          <t>+5,000-10,000 by adding locale/country-scoped passes plus real keyword searches (Low difficulty)</t>
+        </is>
+      </c>
+      <c r="Z111" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA111" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB111" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated Careerjet row's fix: loop fetch_raw() over locale_code values in sources/careerjet.py</t>
         </is>
       </c>
     </row>
@@ -14636,9 +14919,9 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R112" s="8" t="inlineStr">
+        <is>
+          <t>~10,000 (self-capped against a 500,000+ index, matching the self-cap pattern used for Adzuna/Himalayas; report Sec 12 item 4)</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -14649,6 +14932,46 @@
       <c r="T112" t="inlineStr">
         <is>
           <t>Add - authoritative French coverage (Medium effort, OAuth2 registration)</t>
+        </is>
+      </c>
+      <c r="U112" s="8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="V112" s="8" t="inlineStr">
+        <is>
+          <t>N/A - French national service, France-only by design</t>
+        </is>
+      </c>
+      <c r="W112" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; requires free registration and an OAuth2 client-credentials handshake before any pull can happen.</t>
+        </is>
+      </c>
+      <c r="X112" s="8" t="inlineStr">
+        <is>
+          <t>New API integration: register on francetravail.io, implement OAuth2 client-credentials auth, and add location/ROME-code/date filters as a new sources/ module.</t>
+        </is>
+      </c>
+      <c r="Y112" s="8" t="inlineStr">
+        <is>
+          <t>+10,000 (report Sec 12 item 4)</t>
+        </is>
+      </c>
+      <c r="Z112" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA112" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB112" s="8" t="inlineStr">
+        <is>
+          <t>Authentication implementation (OAuth2 client-credentials) + New API integration</t>
         </is>
       </c>
     </row>
@@ -14736,7 +15059,7 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="R113" s="8" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -14749,6 +15072,46 @@
       <c r="T113" t="inlineStr">
         <is>
           <t>Not recommended - scraping-only today (High effort, not advised)</t>
+        </is>
+      </c>
+      <c r="U113" s="8" t="inlineStr">
+        <is>
+          <t>Europe (Other)</t>
+        </is>
+      </c>
+      <c r="V113" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - moot given the report's explicit recommendation against pursuing this source</t>
+        </is>
+      </c>
+      <c r="W113" s="8" t="inlineStr">
+        <is>
+          <t>No technically and legally clean access path exists today. Pan-EU job service (~3M jobs); no supported public pull API today - scraping-only. Not recommended. See report Sec 16 (Europe).</t>
+        </is>
+      </c>
+      <c r="X113" s="8" t="inlineStr">
+        <is>
+          <t>None recommended by the report; revisit only if an official, ToS-clean access path becomes available.</t>
+        </is>
+      </c>
+      <c r="Y113" s="8" t="inlineStr">
+        <is>
+          <t>0 - not recommended for integration</t>
+        </is>
+      </c>
+      <c r="Z113" s="8" t="inlineStr">
+        <is>
+          <t>N/A (not advised regardless of effort)</t>
+        </is>
+      </c>
+      <c r="AA113" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB113" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API / not recommended per report)</t>
         </is>
       </c>
     </row>
@@ -14836,9 +15199,9 @@
       <c r="Q114" t="n">
         <v>2001</v>
       </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>22,000-42,000</t>
+      <c r="R114" s="8" t="inlineStr">
+        <is>
+          <t>22,000-42,000 (same self-capped ceiling as the existing Adzuna integration, shared across all countries queried)</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -14849,6 +15212,46 @@
       <c r="T114" t="inlineStr">
         <is>
           <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="U114" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried by this project; Adzuna's index spans France, Spain, Netherlands, Italy, Poland, Austria and more</t>
+        </is>
+      </c>
+      <c r="V114" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-region opportunity for the already-integrated Adzuna provider - these countries are reachable today with the existing app_id/app_key, simply unqueried</t>
+        </is>
+      </c>
+      <c r="W114" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - same key, same fix as the Canada/SEA/LATAM Adzuna rows: sources/adzuna.py only loops over one hardcoded country.</t>
+        </is>
+      </c>
+      <c r="X114" s="8" t="inlineStr">
+        <is>
+          <t>Configuration/small code change: add fr, es, nl, it, pl, at to the same COUNTRIES list proposed for Canada/UK - one code change covers all of these at once.</t>
+        </is>
+      </c>
+      <c r="Y114" s="8" t="inlineStr">
+        <is>
+          <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="Z114" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA114" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB114" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated Adzuna row's fix: replace COUNTRY = "us" with a loop over a COUNTRIES list in sources/adzuna.py</t>
         </is>
       </c>
     </row>
@@ -14936,9 +15339,9 @@
       <c r="Q115" t="n">
         <v>0</v>
       </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R115" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (large aggregate volume, but no single documented ceiling; see the combined Job Bank CA/NCS India +20,000-50,000 estimate, report Sec 12 item 10)</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -14949,6 +15352,46 @@
       <c r="T115" t="inlineStr">
         <is>
           <t>Investigate - authoritative but freshness-limited (Medium-High effort, ETL)</t>
+        </is>
+      </c>
+      <c r="U115" s="8" t="inlineStr">
+        <is>
+          <t>India (national aggregate vacancy data)</t>
+        </is>
+      </c>
+      <c r="V115" s="8" t="inlineStr">
+        <is>
+          <t>N/A - India-only government service</t>
+        </is>
+      </c>
+      <c r="W115" s="8" t="inlineStr">
+        <is>
+          <t>No live developer API - only a periodic bulk dataset published on data.gov.in, which needs its own ETL ingestion path this project doesn't currently have.</t>
+        </is>
+      </c>
+      <c r="X115" s="8" t="inlineStr">
+        <is>
+          <t>Custom connector: build a bulk-dataset ETL job against data.gov.in instead of a live API pull; freshness will be poor (periodic) regardless of engineering effort.</t>
+        </is>
+      </c>
+      <c r="Y115" s="8" t="inlineStr">
+        <is>
+          <t>+20,000-50,000 combined with Job Bank Canada (report Sec 12 item 10); India-only share not separately broken out</t>
+        </is>
+      </c>
+      <c r="Z115" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA115" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB115" s="8" t="inlineStr">
+        <is>
+          <t>Custom connector (periodic bulk-dataset ETL, a new ingestion pattern for this project)</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15479,7 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="R116" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15049,6 +15492,46 @@
       <c r="T116" t="inlineStr">
         <is>
           <t>Not applicable - no public API; internal endpoint is a ToS grey area</t>
+        </is>
+      </c>
+      <c r="U116" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V116" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W116" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No official public API; internal v2 endpoint is undocumented and a ToS grey area. Not recommended. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X116" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y116" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z116" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA116" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB116" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15619,7 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="R117" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15149,6 +15632,46 @@
       <c r="T117" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U117" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V117" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W117" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No official public API, scraping only. Not recommended. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X117" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y117" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z117" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA117" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB117" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -15236,7 +15759,7 @@
       <c r="Q118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="R118" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15249,6 +15772,46 @@
       <c r="T118" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U118" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V118" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W118" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Blue-collar-focused board; no public API. Not recommended. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X118" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y118" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z118" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA118" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB118" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -15336,9 +15899,9 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R119" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (huge underlying volume, not accessible)</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -15349,6 +15912,46 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>Not applicable for this project - enterprise/partner access only</t>
+        </is>
+      </c>
+      <c r="U119" s="8" t="inlineStr">
+        <is>
+          <t>Global, incl. India</t>
+        </is>
+      </c>
+      <c r="V119" s="8" t="inlineStr">
+        <is>
+          <t>Already global - any region gain would come from partner-tier access, not from a region-specific integration</t>
+        </is>
+      </c>
+      <c r="W119" s="8" t="inlineStr">
+        <is>
+          <t>No open jobs API at any tier - only partner/enterprise OAuth access, which this project does not have.</t>
+        </is>
+      </c>
+      <c r="X119" s="8" t="inlineStr">
+        <is>
+          <t>Would require applying for and being granted LinkedIn partner status; not a pure engineering task and unlikely to be approved for a hobby/small aggregator.</t>
+        </is>
+      </c>
+      <c r="Y119" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (not accessible without partner status)</t>
+        </is>
+      </c>
+      <c r="Z119" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA119" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB119" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (LinkedIn partner program - unlikely to be approved for this project's scale)</t>
         </is>
       </c>
     </row>
@@ -15436,9 +16039,9 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R120" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (huge underlying volume, not accessible)</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -15449,6 +16052,46 @@
       <c r="T120" t="inlineStr">
         <is>
           <t>Not applicable for this project - enterprise/partner access only</t>
+        </is>
+      </c>
+      <c r="U120" s="8" t="inlineStr">
+        <is>
+          <t>Global, incl. India</t>
+        </is>
+      </c>
+      <c r="V120" s="8" t="inlineStr">
+        <is>
+          <t>Already global - the deprecated Publisher API previously covered all Indeed markets</t>
+        </is>
+      </c>
+      <c r="W120" s="8" t="inlineStr">
+        <is>
+          <t>The old consumer-search Publisher API is deprecated; only partner/commercial (Sponsored Jobs) access remains.</t>
+        </is>
+      </c>
+      <c r="X120" s="8" t="inlineStr">
+        <is>
+          <t>Would require a commercial partnership with Indeed; not aligned with this project's free-source model.</t>
+        </is>
+      </c>
+      <c r="Y120" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (not accessible without a commercial partnership)</t>
+        </is>
+      </c>
+      <c r="Z120" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA120" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB120" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (commercial partnership required)</t>
         </is>
       </c>
     </row>
@@ -15536,9 +16179,9 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R121" s="8" t="inlineStr">
+        <is>
+          <t>Budget-dependent, potentially 50,000+ (shared global index with row 106; report Sec 12 item 7)</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -15549,6 +16192,46 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>Add if budget allows (Low effort, paid)</t>
+        </is>
+      </c>
+      <c r="U121" s="8" t="inlineStr">
+        <is>
+          <t>Global, ATS-sourced, incl. India (same index as the US row)</t>
+        </is>
+      </c>
+      <c r="V121" s="8" t="inlineStr">
+        <is>
+          <t>Already global - one integration would cover India alongside every other target region</t>
+        </is>
+      </c>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; requires a paid RapidAPI subscription (free trial only).</t>
+        </is>
+      </c>
+      <c r="X121" s="8" t="inlineStr">
+        <is>
+          <t>Same New API integration as the US row (rows 106) - a single connector serves all regions including India, so this is not a separate engineering effort.</t>
+        </is>
+      </c>
+      <c r="Y121" s="8" t="inlineStr">
+        <is>
+          <t>+50,000+ (budget-bound, shared with the US row; report Sec 12 item 7)</t>
+        </is>
+      </c>
+      <c r="Z121" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA121" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB121" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (same connector as row 106 - not a separate build for India specifically)</t>
         </is>
       </c>
     </row>
@@ -15636,9 +16319,9 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R122" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (enterprise scale play; budget-dependent, shared with row 107)</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -15649,6 +16332,46 @@
       <c r="T122" t="inlineStr">
         <is>
           <t>Enterprise-only scale play, cost-gated (Medium effort)</t>
+        </is>
+      </c>
+      <c r="U122" s="8" t="inlineStr">
+        <is>
+          <t>Global multi-source dataset, incl. India (same index as the US row)</t>
+        </is>
+      </c>
+      <c r="V122" s="8" t="inlineStr">
+        <is>
+          <t>Already global - one integration would cover India alongside every other target region</t>
+        </is>
+      </c>
+      <c r="W122" s="8" t="inlineStr">
+        <is>
+          <t>Same as the US row: enterprise-only paid plan with no free tier.</t>
+        </is>
+      </c>
+      <c r="X122" s="8" t="inlineStr">
+        <is>
+          <t>Same enterprise procurement + integration as row 107 - not a separate build for India specifically.</t>
+        </is>
+      </c>
+      <c r="Y122" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (budget-dependent enterprise plan)</t>
+        </is>
+      </c>
+      <c r="Z122" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA122" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB122" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (procurement + New API integration; same connector as row 107)</t>
         </is>
       </c>
     </row>
@@ -15736,9 +16459,9 @@
       <c r="Q123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R123" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (volume not published)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -15749,6 +16472,46 @@
       <c r="T123" t="inlineStr">
         <is>
           <t>Add if budget allows (Low effort, paid)</t>
+        </is>
+      </c>
+      <c r="U123" s="8" t="inlineStr">
+        <is>
+          <t>India (incl. Naukri/Monster-sourced feeds)</t>
+        </is>
+      </c>
+      <c r="V123" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - pricing/coverage details for other regions not published</t>
+        </is>
+      </c>
+      <c r="W123" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; pricing is custom/undisclosed, and documentation availability is unconfirmed.</t>
+        </is>
+      </c>
+      <c r="X123" s="8" t="inlineStr">
+        <is>
+          <t>Investigate: request pricing/docs from JobsPikr before scoping an integration; treat as budget-gated like Fantastic Jobs/Coresignal.</t>
+        </is>
+      </c>
+      <c r="Y123" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (custom pricing, volume not published)</t>
+        </is>
+      </c>
+      <c r="Z123" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA123" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB123" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (pending pricing/docs confirmation)</t>
         </is>
       </c>
     </row>
@@ -15838,9 +16601,9 @@
           <t>Unknown - folds into the combined 1,125-job SerpApi+OpenWeb Ninja+Careerjet total; not separable (see Notes)</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>Unknown (metered; budget-dependent, ~200/mo ceiling)</t>
+      <c r="R124" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (metered; budget-dependent, ~200/mo ceiling shared across all OpenWeb Ninja queries including this one)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -15851,6 +16614,46 @@
       <c r="T124" t="inlineStr">
         <is>
           <t>Reallocate quota toward country-filtered (e.g. India) queries (Low difficulty, budget-bound)</t>
+        </is>
+      </c>
+      <c r="U124" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried with an India-scoped pass; the already-integrated OpenWeb Ninja key covers this via the country param</t>
+        </is>
+      </c>
+      <c r="V124" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-scope opportunity for the already-integrated OpenWeb Ninja (JSearch) provider</t>
+        </is>
+      </c>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - OpenWeb Ninja is already integrated; the current implementation runs one wildcard query instead of a country-filtered one, and is capped at 200 requests/month regardless.</t>
+        </is>
+      </c>
+      <c r="X124" s="8" t="inlineStr">
+        <is>
+          <t>Small code change: add a country="in" (or similar) param to the existing query in sources/openwebninja.py, reallocating a slice of the existing monthly quota toward India instead of the generic wildcard.</t>
+        </is>
+      </c>
+      <c r="Y124" s="8" t="inlineStr">
+        <is>
+          <t>Shares in the combined +10,000-20,000 India bucket (ATS slugs + India-scoped metered-API queries; report Sec 12 item 9) - exact split not separately broken out</t>
+        </is>
+      </c>
+      <c r="Z124" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA124" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB124" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated OpenWeb Ninja row's fix: add country/location params in sources/openwebninja.py</t>
         </is>
       </c>
     </row>
@@ -15940,9 +16743,9 @@
           <t>Unknown - folds into the combined 1,125-job SerpApi+OpenWeb Ninja+Careerjet total; not separable (see Notes)</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>Unknown (metered; budget-dependent, ~2,500/mo ceiling)</t>
+      <c r="R125" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (metered; budget-dependent, ~2,500/mo ceiling shared across all SerpApi queries including this one)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -15953,6 +16756,46 @@
       <c r="T125" t="inlineStr">
         <is>
           <t>Reallocate quota to targeted location/date-filtered queries (Low difficulty, budget-bound)</t>
+        </is>
+      </c>
+      <c r="U125" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried with an India-scoped pass; the already-integrated SerpApi key covers this via the location param</t>
+        </is>
+      </c>
+      <c r="V125" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-scope opportunity for the already-integrated SerpApi (Google Jobs) provider</t>
+        </is>
+      </c>
+      <c r="W125" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - SerpApi is already integrated; the current implementation runs one wildcard query instead of a location-filtered one, and is capped at 250 searches/month regardless.</t>
+        </is>
+      </c>
+      <c r="X125" s="8" t="inlineStr">
+        <is>
+          <t>Small code change: add a location value targeting India to the existing query in sources/serpapi.py, reallocating a slice of the existing monthly quota toward India instead of the generic wildcard.</t>
+        </is>
+      </c>
+      <c r="Y125" s="8" t="inlineStr">
+        <is>
+          <t>Shares in the combined +10,000-20,000 India bucket (ATS slugs + India-scoped metered-API queries; report Sec 12 item 9) - exact split not separately broken out</t>
+        </is>
+      </c>
+      <c r="Z125" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA125" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB125" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated SerpApi row's fix: parametrize location/q in sources/serpapi.py</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16883,7 @@
       <c r="Q126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="R126" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16053,6 +16896,46 @@
       <c r="T126" t="inlineStr">
         <is>
           <t>Not applicable - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="U126" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V126" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W126" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. India-origin ATS/HRMS; per-tenant API only, no aggregate feed - not aggregatable for this project. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X126" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y126" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z126" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA126" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB126" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -16140,7 +17023,7 @@
       <c r="Q127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="R127" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16153,6 +17036,46 @@
       <c r="T127" t="inlineStr">
         <is>
           <t>Not applicable - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="U127" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V127" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W127" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. India-origin ATS/HRMS (Freshworks); per-tenant API only, no aggregate feed. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X127" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y127" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z127" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA127" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB127" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -16240,7 +17163,7 @@
       <c r="Q128" t="n">
         <v>0</v>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16253,6 +17176,46 @@
       <c r="T128" t="inlineStr">
         <is>
           <t>Not applicable - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="U128" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V128" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W128" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. India-origin ATS/HRMS; per-tenant application-data API only, no aggregate feed. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X128" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y128" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z128" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA128" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB128" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -16340,7 +17303,7 @@
       <c r="Q129" t="n">
         <v>0</v>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="R129" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16353,6 +17316,46 @@
       <c r="T129" t="inlineStr">
         <is>
           <t>Not applicable - no job-related feed exists</t>
+        </is>
+      </c>
+      <c r="U129" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V129" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W129" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. India-origin HRMS/payroll platform; no job-board feed at all. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X129" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y129" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z129" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA129" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB129" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -16440,7 +17443,7 @@
       <c r="Q130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="R130" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -16453,6 +17456,46 @@
       <c r="T130" t="inlineStr">
         <is>
           <t>Not applicable - no job-related feed exists</t>
+        </is>
+      </c>
+      <c r="U130" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V130" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W130" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. India-origin HRMS/payroll platform; no job feed at all. See report Sec 10 (India subsection).</t>
+        </is>
+      </c>
+      <c r="X130" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y130" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z130" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA130" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB130" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -16540,9 +17583,9 @@
       <c r="Q131" t="n">
         <v>0</v>
       </c>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R131" s="8" t="inlineStr">
+        <is>
+          <t>10,000-20,000 (self-capped pull from ~80,000 available, matching the self-cap pattern used for Adzuna/Himalayas/The Muse; report Sec 12 item 2)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -16553,6 +17596,46 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>Add - Critical, top Singapore/SEA priority (Low effort, no auth)</t>
+        </is>
+      </c>
+      <c r="U131" s="8" t="inlineStr">
+        <is>
+          <t>Singapore (national government job portal)</t>
+        </is>
+      </c>
+      <c r="V131" s="8" t="inlineStr">
+        <is>
+          <t>N/A - Singapore-only by design</t>
+        </is>
+      </c>
+      <c r="W131" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; otherwise no-auth, fully public - the only gap is that no connector has been written.</t>
+        </is>
+      </c>
+      <c r="X131" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (Low effort, no auth): build a sources/mycareersfuture.py module against the v2 endpoint, 100 jobs/page pagination, no credentials required.</t>
+        </is>
+      </c>
+      <c r="Y131" s="8" t="inlineStr">
+        <is>
+          <t>+15,000 (report Sec 12 item 2)</t>
+        </is>
+      </c>
+      <c r="Z131" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA131" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB131" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (no auth required - the single highest-value net-new integration in this audit)</t>
         </is>
       </c>
     </row>
@@ -16640,9 +17723,9 @@
       <c r="Q132" t="n">
         <v>0</v>
       </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R132" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (partner-only; the underlying SEEK-group inventory is very large but inaccessible)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -16653,6 +17736,46 @@
       <c r="T132" t="inlineStr">
         <is>
           <t>Not recommended - scraping-only (High effort, not advised)</t>
+        </is>
+      </c>
+      <c r="U132" s="8" t="inlineStr">
+        <is>
+          <t>Malaysia, Indonesia, Philippines, Singapore, Thailand, Vietnam (SEEK group)</t>
+        </is>
+      </c>
+      <c r="V132" s="8" t="inlineStr">
+        <is>
+          <t>N/A for this project - already covers the full SEA footprint, but only via partner access</t>
+        </is>
+      </c>
+      <c r="W132" s="8" t="inlineStr">
+        <is>
+          <t>No public API - SEEK exposes partner APIs only; the only technical path to this data is scraping, which the report explicitly advises against.</t>
+        </is>
+      </c>
+      <c r="X132" s="8" t="inlineStr">
+        <is>
+          <t>None recommended - the only technical path is scraping, which carries ToS/legal risk and was explicitly ruled out; revisit only if an official partner feed becomes available.</t>
+        </is>
+      </c>
+      <c r="Y132" s="8" t="inlineStr">
+        <is>
+          <t>0 - not recommended for integration</t>
+        </is>
+      </c>
+      <c r="Z132" s="8" t="inlineStr">
+        <is>
+          <t>High (and not advised)</t>
+        </is>
+      </c>
+      <c r="AA132" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB132" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API / scraping required, not recommended)</t>
         </is>
       </c>
     </row>
@@ -16740,9 +17863,9 @@
       <c r="Q133" t="n">
         <v>2001</v>
       </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>22,000-42,000</t>
+      <c r="R133" s="8" t="inlineStr">
+        <is>
+          <t>22,000-42,000 if 'sg' is available (same self-capped ceiling as the existing Adzuna integration); Unknown if not covered by the plan</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -16753,6 +17876,46 @@
       <c r="T133" t="inlineStr">
         <is>
           <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="U133" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried by this project; Adzuna covers Singapore if included in the current plan tier</t>
+        </is>
+      </c>
+      <c r="V133" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-region opportunity for the already-integrated Adzuna provider, contingent on the existing key's plan actually including 'sg'</t>
+        </is>
+      </c>
+      <c r="W133" s="8" t="inlineStr">
+        <is>
+          <t>Needs verification that the existing Adzuna plan includes the 'sg' country index before assuming this is a config-only change like the Canada/UK/Europe/LATAM Adzuna rows.</t>
+        </is>
+      </c>
+      <c r="X133" s="8" t="inlineStr">
+        <is>
+          <t>Configuration/small code change if 'sg' is confirmed available on the existing plan: add it to the same COUNTRIES list proposed for Canada/UK/Europe/LATAM.</t>
+        </is>
+      </c>
+      <c r="Y133" s="8" t="inlineStr">
+        <is>
+          <t>Part of the +19,999-39,999 combined Adzuna multi-country opportunity, contingent on plan coverage for 'sg'</t>
+        </is>
+      </c>
+      <c r="Z133" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA133" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB133" s="8" t="inlineStr">
+        <is>
+          <t>Small code change (same COUNTRIES-list fix as the other Adzuna rows), pending confirmation that the plan covers 'sg'</t>
         </is>
       </c>
     </row>
@@ -16840,9 +18003,9 @@
       <c r="Q134" t="n">
         <v>0</v>
       </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R134" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (est. 5,000-20,000 per research, but the API's existence/pricing is unverified)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -16853,6 +18016,46 @@
       <c r="T134" t="inlineStr">
         <is>
           <t>Investigate/Add - one LATAM board with a confirmed real API (Low-Medium effort)</t>
+        </is>
+      </c>
+      <c r="U134" s="8" t="inlineStr">
+        <is>
+          <t>LATAM (tech-focused, remote-friendly)</t>
+        </is>
+      </c>
+      <c r="V134" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - primarily LATAM-wide per its own positioning, but exact country coverage unverified</t>
+        </is>
+      </c>
+      <c r="W134" s="8" t="inlineStr">
+        <is>
+          <t>The site advertises a public API and ATS integrations, but auth/pricing/documentation have not been independently verified - this needs confirmation before scoping an integration.</t>
+        </is>
+      </c>
+      <c r="X134" s="8" t="inlineStr">
+        <is>
+          <t>Investigate first (confirm the API's auth model and pricing), then a New API integration if it checks out - one of the few LATAM boards with any documented API at all.</t>
+        </is>
+      </c>
+      <c r="Y134" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (pending API verification)</t>
+        </is>
+      </c>
+      <c r="Z134" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA134" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB134" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (pending verification of auth/pricing/docs)</t>
         </is>
       </c>
     </row>
@@ -16940,9 +18143,9 @@
       <c r="Q135" t="n">
         <v>2001</v>
       </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>22,000-42,000</t>
+      <c r="R135" s="8" t="inlineStr">
+        <is>
+          <t>22,000-42,000 (same self-capped ceiling as the existing Adzuna integration, shared across all countries queried)</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -16953,6 +18156,46 @@
       <c r="T135" t="inlineStr">
         <is>
           <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="U135" s="8" t="inlineStr">
+        <is>
+          <t>N/A - not yet queried by this project; Adzuna covers Brazil and Mexico, the two largest LATAM markets</t>
+        </is>
+      </c>
+      <c r="V135" s="8" t="inlineStr">
+        <is>
+          <t>This row IS the additional-region opportunity for the already-integrated Adzuna provider - br/mx are reachable today with the existing app_id/app_key, simply unqueried</t>
+        </is>
+      </c>
+      <c r="W135" s="8" t="inlineStr">
+        <is>
+          <t>Zero technical gap - same key, same fix as the Canada/UK/Europe Adzuna rows. This also adds real in-country LATAM volume, since most of this project's current LATAM jobs are remote-nearshore rather than location-specific.</t>
+        </is>
+      </c>
+      <c r="X135" s="8" t="inlineStr">
+        <is>
+          <t>Configuration/small code change: add br and mx to the same COUNTRIES list proposed for Canada/UK/Europe.</t>
+        </is>
+      </c>
+      <c r="Y135" s="8" t="inlineStr">
+        <is>
+          <t>+19,999-39,999 by querying the 10+ additional countries the existing key already covers (Low difficulty) - single highest-leverage lever in this report</t>
+        </is>
+      </c>
+      <c r="Z135" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA135" s="8" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="AB135" s="8" t="inlineStr">
+        <is>
+          <t>Small code change - identical to the Integrated Adzuna row's fix: replace COUNTRY = "us" with a loop over a COUNTRIES list in sources/adzuna.py</t>
         </is>
       </c>
     </row>
@@ -17040,7 +18283,7 @@
       <c r="Q136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="R136" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17053,6 +18296,46 @@
       <c r="T136" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U136" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="V136" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W136" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Canada).</t>
+        </is>
+      </c>
+      <c r="X136" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y136" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z136" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA136" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB136" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17140,7 +18423,7 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="R137" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17153,6 +18436,46 @@
       <c r="T137" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U137" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="V137" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W137" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Canada).</t>
+        </is>
+      </c>
+      <c r="X137" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y137" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z137" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA137" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB137" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17240,9 +18563,9 @@
       <c r="Q138" t="n">
         <v>0</v>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R138" s="8" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -17253,6 +18576,46 @@
       <c r="T138" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U138" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="V138" s="8" t="inlineStr">
+        <is>
+          <t>N/A - Canada-only board</t>
+        </is>
+      </c>
+      <c r="W138" s="8" t="inlineStr">
+        <is>
+          <t>No public read API - a paid Partner/Employer API exists but only for posting jobs (XML insertion), not for reading/aggregating listings.</t>
+        </is>
+      </c>
+      <c r="X138" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via a read-only aggregator model; the only door (posting API) doesn't serve this project's use case.</t>
+        </is>
+      </c>
+      <c r="Y138" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable via a read API</t>
+        </is>
+      </c>
+      <c r="Z138" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA138" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB138" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API - posting-only partner feed exists, not a read/search API)</t>
         </is>
       </c>
     </row>
@@ -17340,9 +18703,9 @@
       <c r="Q139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R139" s="8" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -17353,6 +18716,46 @@
       <c r="T139" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U139" s="8" t="inlineStr">
+        <is>
+          <t>Canada (plus a global aggregator footprint)</t>
+        </is>
+      </c>
+      <c r="V139" s="8" t="inlineStr">
+        <is>
+          <t>N/A for this project - Talent.com aggregates globally, but the only access path (Publisher XML feed / self-serve backfill) is a paid revenue-share partnership, not a public read API</t>
+        </is>
+      </c>
+      <c r="W139" s="8" t="inlineStr">
+        <is>
+          <t>No self-serve public read API - a Publisher XML feed and backfill API exist only via a paid/revenue-share commercial partnership.</t>
+        </is>
+      </c>
+      <c r="X139" s="8" t="inlineStr">
+        <is>
+          <t>Would require negotiating a commercial revenue-share partnership before any integration work; not a pure engineering task.</t>
+        </is>
+      </c>
+      <c r="Y139" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - partner-gated</t>
+        </is>
+      </c>
+      <c r="Z139" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA139" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB139" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (revenue-share partnership required, then New API integration)</t>
         </is>
       </c>
     </row>
@@ -17440,7 +18843,7 @@
       <c r="Q140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="R140" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17453,6 +18856,46 @@
       <c r="T140" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U140" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="V140" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W140" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Canada).</t>
+        </is>
+      </c>
+      <c r="X140" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y140" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z140" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA140" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB140" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17540,9 +18983,9 @@
       <c r="Q141" t="n">
         <v>0</v>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R141" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (paid API, not evaluated - out of scope per report)</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -17553,6 +18996,46 @@
       <c r="T141" t="inlineStr">
         <is>
           <t>Not recommended - paid, out of scope for this project</t>
+        </is>
+      </c>
+      <c r="U141" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="V141" s="8" t="inlineStr">
+        <is>
+          <t>Lightcast also covers the US and other markets, but this project has scoped it out entirely (paid, out of scope)</t>
+        </is>
+      </c>
+      <c r="W141" s="8" t="inlineStr">
+        <is>
+          <t>No technical gap - a documented commercial API exists. The only reason it isn't integrated is that it's paid, and the report scopes this project to free/near-free sources.</t>
+        </is>
+      </c>
+      <c r="X141" s="8" t="inlineStr">
+        <is>
+          <t>Would be a straightforward paid-API integration if budget were approved - a business decision, not an engineering blocker.</t>
+        </is>
+      </c>
+      <c r="Y141" s="8" t="inlineStr">
+        <is>
+          <t>0 - not recommended for integration (out of scope, paid)</t>
+        </is>
+      </c>
+      <c r="Z141" s="8" t="inlineStr">
+        <is>
+          <t>Low (technically easy; not pursued for budget/scope reasons)</t>
+        </is>
+      </c>
+      <c r="AA141" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB141" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (not pursued - paid, out of scope per report)</t>
         </is>
       </c>
     </row>
@@ -17640,7 +19123,7 @@
       <c r="Q142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="R142" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17653,6 +19136,46 @@
       <c r="T142" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U142" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="V142" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W142" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (United Kingdom). Access model corrected to Enterprise: partner-only paid access via the StepStone group. See report Sec 18.2.</t>
+        </is>
+      </c>
+      <c r="X142" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y142" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z142" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA142" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB142" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17740,7 +19263,7 @@
       <c r="Q143" t="n">
         <v>0</v>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="R143" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17753,6 +19276,46 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U143" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="V143" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W143" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (United Kingdom). Access model corrected to Enterprise: a paid Partner/Employer API exists (posting + CV search), not job aggregation. See report Sec 18.2.</t>
+        </is>
+      </c>
+      <c r="X143" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y143" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z143" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA143" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB143" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17840,7 +19403,7 @@
       <c r="Q144" t="n">
         <v>0</v>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="R144" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17853,6 +19416,46 @@
       <c r="T144" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U144" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="V144" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W144" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (United Kingdom). Access model corrected to Enterprise: partner-only paid access via the StepStone group. See report Sec 18.2.</t>
+        </is>
+      </c>
+      <c r="X144" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y144" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z144" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA144" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB144" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -17940,7 +19543,7 @@
       <c r="Q145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="R145" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -17953,6 +19556,46 @@
       <c r="T145" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U145" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="V145" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W145" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (United Kingdom). Access model corrected to Enterprise: partner-only paid access via the StepStone group. See report Sec 18.2.</t>
+        </is>
+      </c>
+      <c r="X145" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y145" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z145" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA145" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB145" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18040,7 +19683,7 @@
       <c r="Q146" t="n">
         <v>0</v>
       </c>
-      <c r="R146" t="inlineStr">
+      <c r="R146" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18053,6 +19696,46 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U146" s="8" t="inlineStr">
+        <is>
+          <t>Europe (Other)</t>
+        </is>
+      </c>
+      <c r="V146" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W146" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Europe (Other)). Access model corrected to Enterprise: a paid Enterprise/Partner API exists (api.stepstone.com, ATS/Talentsoft ecosystem). See report Sec 18.3.</t>
+        </is>
+      </c>
+      <c r="X146" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y146" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z146" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA146" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB146" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18140,7 +19823,7 @@
       <c r="Q147" t="n">
         <v>0</v>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="R147" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18153,6 +19836,46 @@
       <c r="T147" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U147" s="8" t="inlineStr">
+        <is>
+          <t>Europe (Other)</t>
+        </is>
+      </c>
+      <c r="V147" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W147" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Europe (Other)). Access model corrected to Enterprise: partner/enterprise paid access only (legacy public API deprecated). See report Sec 18.3.</t>
+        </is>
+      </c>
+      <c r="X147" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y147" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z147" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA147" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB147" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18240,7 +19963,7 @@
       <c r="Q148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="R148" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18253,6 +19976,46 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U148" s="8" t="inlineStr">
+        <is>
+          <t>Europe (Other)</t>
+        </is>
+      </c>
+      <c r="V148" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W148" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Europe (Other)). Access model corrected to Enterprise: a Publisher/Partner backfill feed exists via paid/revenue-share commercial deal only. See report Sec 18.3.</t>
+        </is>
+      </c>
+      <c r="X148" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y148" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z148" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA148" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB148" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18340,7 +20103,7 @@
       <c r="Q149" t="n">
         <v>0</v>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="R149" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18353,6 +20116,46 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U149" s="8" t="inlineStr">
+        <is>
+          <t>Europe (Other)</t>
+        </is>
+      </c>
+      <c r="V149" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W149" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Europe (Other)).</t>
+        </is>
+      </c>
+      <c r="X149" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y149" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z149" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA149" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB149" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18440,7 +20243,7 @@
       <c r="Q150" t="n">
         <v>0</v>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="R150" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18453,6 +20256,46 @@
       <c r="T150" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U150" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="V150" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (LATAM).</t>
+        </is>
+      </c>
+      <c r="X150" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y150" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z150" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA150" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB150" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18540,7 +20383,7 @@
       <c r="Q151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="R151" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18553,6 +20396,46 @@
       <c r="T151" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U151" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="V151" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W151" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (LATAM).</t>
+        </is>
+      </c>
+      <c r="X151" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y151" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z151" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA151" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB151" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18640,7 +20523,7 @@
       <c r="Q152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="R152" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18653,6 +20536,46 @@
       <c r="T152" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U152" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="V152" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W152" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (LATAM).</t>
+        </is>
+      </c>
+      <c r="X152" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y152" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z152" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA152" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB152" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18740,7 +20663,7 @@
       <c r="Q153" t="n">
         <v>0</v>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="R153" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18753,6 +20676,46 @@
       <c r="T153" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U153" s="8" t="inlineStr">
+        <is>
+          <t>Singapore/SEA</t>
+        </is>
+      </c>
+      <c r="V153" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W153" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Singapore/SEA).</t>
+        </is>
+      </c>
+      <c r="X153" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y153" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z153" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA153" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB153" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18840,7 +20803,7 @@
       <c r="Q154" t="n">
         <v>0</v>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="R154" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18853,6 +20816,46 @@
       <c r="T154" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U154" s="8" t="inlineStr">
+        <is>
+          <t>Singapore/SEA</t>
+        </is>
+      </c>
+      <c r="V154" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W154" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Explicitly evaluated and ruled out - closed with no public API (or paid partner/posting channel only). See report Sec 11 (Singapore/SEA).</t>
+        </is>
+      </c>
+      <c r="X154" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y154" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z154" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA154" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB154" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -18940,9 +20943,9 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R155" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (volume not published)</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -18953,6 +20956,46 @@
       <c r="T155" t="inlineStr">
         <is>
           <t>Low priority - remote-only, overlaps existing remote feeds (Low effort if pursued)</t>
+        </is>
+      </c>
+      <c r="U155" s="8" t="inlineStr">
+        <is>
+          <t>Remote jobs, US-heavy</t>
+        </is>
+      </c>
+      <c r="V155" s="8" t="inlineStr">
+        <is>
+          <t>Remote-only by nature; not region-scoped beyond that</t>
+        </is>
+      </c>
+      <c r="W155" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; otherwise no-key/no-signup barrier at all - the only gap is that nobody has written the connector.</t>
+        </is>
+      </c>
+      <c r="X155" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (Low effort, no auth) - lowest priority because it overlaps existing RemoteOK/Himalayas remote feeds and would mostly add duplication rather than reach.</t>
+        </is>
+      </c>
+      <c r="Y155" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (likely small; overlaps existing remote feeds per Notes)</t>
+        </is>
+      </c>
+      <c r="Z155" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA155" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB155" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (no auth, but low expected marginal value)</t>
         </is>
       </c>
     </row>
@@ -19040,9 +21083,9 @@
       <c r="Q156" t="n">
         <v>0</v>
       </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R156" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (per-tenant; no aggregate index - depends entirely on how many companies are curated)</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -19053,6 +21096,46 @@
       <c r="T156" t="inlineStr">
         <is>
           <t>Investigate - new integration, high enterprise-India value (Medium-Hard effort)</t>
+        </is>
+      </c>
+      <c r="U156" s="8" t="inlineStr">
+        <is>
+          <t>Global, per-tenant career sites, incl. India</t>
+        </is>
+      </c>
+      <c r="V156" s="8" t="inlineStr">
+        <is>
+          <t>Any region where a Workday-hosted company career site is curated - not a queryable API region, but a per-company one like the six existing ATS providers</t>
+        </is>
+      </c>
+      <c r="W156" s="8" t="inlineStr">
+        <is>
+          <t>No aggregate index exists; each company's Workday career site (CxS endpoint) must be discovered and added individually, the same curated-company model as Greenhouse/Lever/Ashby/SmartRecruiters/Workable/Teamtailor, but with no existing connector for this ATS in this project.</t>
+        </is>
+      </c>
+      <c r="X156" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (Custom connector): build a sources/workday.py module that fetches each curated company's public CxS JSON endpoint, following the existing per-company ATS pattern; then curate India-HQ (and other target-region) company slugs.</t>
+        </is>
+      </c>
+      <c r="Y156" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (depends on curated company count; would meaningfully close the ATS-coverage gap for large Indian enterprises per Notes)</t>
+        </is>
+      </c>
+      <c r="Z156" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA156" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB156" s="8" t="inlineStr">
+        <is>
+          <t>Custom connector (new ATS integration, following the existing Greenhouse/Lever/etc. per-company pattern) + company-slug discovery</t>
         </is>
       </c>
     </row>
@@ -19140,7 +21223,7 @@
       <c r="Q157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="R157" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19153,6 +21236,46 @@
       <c r="T157" t="inlineStr">
         <is>
           <t>Not applicable - consumes listings, does not publish a feed</t>
+        </is>
+      </c>
+      <c r="U157" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V157" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W157" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Staffing ATS that aggregates boards inward; does not publish an outward feed. See report Sec 16.3 (India).</t>
+        </is>
+      </c>
+      <c r="X157" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y157" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z157" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA157" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB157" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19240,7 +21363,7 @@
       <c r="Q158" t="n">
         <v>0</v>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="R158" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19253,6 +21376,46 @@
       <c r="T158" t="inlineStr">
         <is>
           <t>Not applicable - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="U158" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V158" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W158" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. Per-customer API only, no aggregate feed. See report Sec 16.3 (India).</t>
+        </is>
+      </c>
+      <c r="X158" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y158" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z158" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA158" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB158" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -19340,7 +21503,7 @@
       <c r="Q159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="inlineStr">
+      <c r="R159" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19353,6 +21516,46 @@
       <c r="T159" t="inlineStr">
         <is>
           <t>Not applicable - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="U159" s="8" t="inlineStr">
+        <is>
+          <t>Remote/Global</t>
+        </is>
+      </c>
+      <c r="V159" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W159" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. US-origin ATS; per-customer API plus some public career pages, evaluated as a potential source of Indian listings but found limited/per-tenant. See report Sec 16.3 (India).</t>
+        </is>
+      </c>
+      <c r="X159" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y159" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z159" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA159" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB159" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -19440,7 +21643,7 @@
       <c r="Q160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="inlineStr">
+      <c r="R160" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19453,6 +21656,46 @@
       <c r="T160" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U160" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V160" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W160" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No official public API; consumer job board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X160" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y160" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z160" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA160" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB160" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19540,7 +21783,7 @@
       <c r="Q161" t="n">
         <v>0</v>
       </c>
-      <c r="R161" t="inlineStr">
+      <c r="R161" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19553,6 +21796,46 @@
       <c r="T161" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U161" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V161" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W161" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No official public API; consumer job board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X161" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y161" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z161" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA161" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB161" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19640,7 +21923,7 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
-      <c r="R162" t="inlineStr">
+      <c r="R162" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19653,6 +21936,46 @@
       <c r="T162" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U162" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V162" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W162" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; blue-collar-focused board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X162" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y162" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z162" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA162" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB162" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19740,7 +22063,7 @@
       <c r="Q163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="inlineStr">
+      <c r="R163" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19753,6 +22076,46 @@
       <c r="T163" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U163" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V163" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W163" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; small tech-focused board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X163" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y163" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z163" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA163" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB163" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19840,7 +22203,7 @@
       <c r="Q164" t="n">
         <v>0</v>
       </c>
-      <c r="R164" t="inlineStr">
+      <c r="R164" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19853,6 +22216,46 @@
       <c r="T164" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U164" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V164" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W164" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; medium tech-focused board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X164" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y164" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z164" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA164" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB164" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -19940,7 +22343,7 @@
       <c r="Q165" t="n">
         <v>0</v>
       </c>
-      <c r="R165" t="inlineStr">
+      <c r="R165" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19953,6 +22356,46 @@
       <c r="T165" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U165" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V165" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W165" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; Info Edge property (tech-focused). See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X165" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y165" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z165" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA165" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB165" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20040,7 +22483,7 @@
       <c r="Q166" t="n">
         <v>0</v>
       </c>
-      <c r="R166" t="inlineStr">
+      <c r="R166" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20053,6 +22496,46 @@
       <c r="T166" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U166" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V166" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W166" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; Info Edge property (management-focused). See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X166" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y166" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z166" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA166" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB166" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20140,9 +22623,9 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R167" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (medium fresher/graduate board; feed liveness unverified)</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -20153,6 +22636,46 @@
       <c r="T167" t="inlineStr">
         <is>
           <t>Investigate - only India consumer board with a historical feed (Low-Med effort)</t>
+        </is>
+      </c>
+      <c r="U167" s="8" t="inlineStr">
+        <is>
+          <t>India (fresher/graduate jobs)</t>
+        </is>
+      </c>
+      <c r="V167" s="8" t="inlineStr">
+        <is>
+          <t>N/A - India-focused board</t>
+        </is>
+      </c>
+      <c r="W167" s="8" t="inlineStr">
+        <is>
+          <t>The only India consumer board with a historical RSS/XML feed, but whether it is still live and unchanged needs verification before building against it.</t>
+        </is>
+      </c>
+      <c r="X167" s="8" t="inlineStr">
+        <is>
+          <t>Investigate first (confirm the feed is still live and its current format), then a small New API integration (RSS/XML parsing, similar in shape to sources/teamtailor.py) if confirmed.</t>
+        </is>
+      </c>
+      <c r="Y167" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (feed liveness unverified)</t>
+        </is>
+      </c>
+      <c r="Z167" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA167" s="8" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="AB167" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (RSS/XML, pending liveness verification)</t>
         </is>
       </c>
     </row>
@@ -20240,7 +22763,7 @@
       <c r="Q168" t="n">
         <v>0</v>
       </c>
-      <c r="R168" t="inlineStr">
+      <c r="R168" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20253,6 +22776,46 @@
       <c r="T168" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U168" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V168" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W168" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; large intern/fresher board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X168" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y168" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z168" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA168" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB168" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20340,7 +22903,7 @@
       <c r="Q169" t="n">
         <v>0</v>
       </c>
-      <c r="R169" t="inlineStr">
+      <c r="R169" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20353,6 +22916,46 @@
       <c r="T169" t="inlineStr">
         <is>
           <t>Not applicable - not a job-listing API</t>
+        </is>
+      </c>
+      <c r="U169" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V169" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W169" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public jobs API; primarily an assessment/competition platform, not a job-listing API. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X169" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y169" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z169" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA169" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB169" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20440,7 +23043,7 @@
       <c r="Q170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="inlineStr">
+      <c r="R170" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20453,6 +23056,46 @@
       <c r="T170" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U170" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V170" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W170" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No official public API (formerly AngelList); startup-focused board. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X170" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y170" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z170" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA170" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB170" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20540,9 +23183,9 @@
       <c r="Q171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R171" s="8" t="inlineStr">
+        <is>
+          <t>Small (tiny community-tech volume, per existing Notes)</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -20553,6 +23196,46 @@
       <c r="T171" t="inlineStr">
         <is>
           <t>Investigate - tiny volume, low priority (Low effort)</t>
+        </is>
+      </c>
+      <c r="U171" s="8" t="inlineStr">
+        <is>
+          <t>India (small community tech board)</t>
+        </is>
+      </c>
+      <c r="V171" s="8" t="inlineStr">
+        <is>
+          <t>N/A - India-focused, tiny community board</t>
+        </is>
+      </c>
+      <c r="W171" s="8" t="inlineStr">
+        <is>
+          <t>Public listings feed reportedly exists, but liveness/format needs verification; volume is tiny regardless.</t>
+        </is>
+      </c>
+      <c r="X171" s="8" t="inlineStr">
+        <is>
+          <t>Investigate first; if confirmed live, a small New API integration - but low priority given the tiny expected volume.</t>
+        </is>
+      </c>
+      <c r="Y171" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (tiny volume expected either way)</t>
+        </is>
+      </c>
+      <c r="Z171" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA171" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB171" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (RSS/JSON, pending liveness verification; low expected marginal value)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +23323,7 @@
       <c r="Q172" t="n">
         <v>0</v>
       </c>
-      <c r="R172" t="inlineStr">
+      <c r="R172" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20653,6 +23336,46 @@
       <c r="T172" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U172" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V172" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W172" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public jobs API; primarily an assessment platform with job listings attached. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X172" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y172" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z172" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA172" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB172" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20740,7 +23463,7 @@
       <c r="Q173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="inlineStr">
+      <c r="R173" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20753,6 +23476,46 @@
       <c r="T173" t="inlineStr">
         <is>
           <t>Not applicable - per-college gated, not aggregatable</t>
+        </is>
+      </c>
+      <c r="U173" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V173" s="8" t="inlineStr">
+        <is>
+          <t>N/A - a per-tenant/per-institution credential covers one employer, not a regional index</t>
+        </is>
+      </c>
+      <c r="W173" s="8" t="inlineStr">
+        <is>
+          <t>Access requires a separate credential per employer/tenant - there is no aggregate feed to query regardless of region. Campus-placement platform; per-institution partner access, not aggregatable across colleges. See report Sec 16.2 (India).</t>
+        </is>
+      </c>
+      <c r="X173" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable as an aggregator source: per-tenant access doesn't scale to a multi-employer index without individually onboarding every employer, which this project's model does not do for any other ATS either.</t>
+        </is>
+      </c>
+      <c r="Y173" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not aggregatable across employers</t>
+        </is>
+      </c>
+      <c r="Z173" s="8" t="inlineStr">
+        <is>
+          <t>N/A (per-tenant only - not aggregatable at any effort level)</t>
+        </is>
+      </c>
+      <c r="AA173" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB173" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (per-tenant API only, no aggregate feed)</t>
         </is>
       </c>
     </row>
@@ -20840,7 +23603,7 @@
       <c r="Q174" t="n">
         <v>0</v>
       </c>
-      <c r="R174" t="inlineStr">
+      <c r="R174" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20853,6 +23616,46 @@
       <c r="T174" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U174" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V174" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W174" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Major Indian staffing firm; no public job feed, bulk staffing via own systems. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X174" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y174" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z174" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA174" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB174" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -20940,7 +23743,7 @@
       <c r="Q175" t="n">
         <v>0</v>
       </c>
-      <c r="R175" t="inlineStr">
+      <c r="R175" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20953,6 +23756,46 @@
       <c r="T175" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U175" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V175" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W175" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Major Indian staffing firm; no public job feed, own portal only. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X175" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y175" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z175" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA175" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB175" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21040,7 +23883,7 @@
       <c r="Q176" t="n">
         <v>0</v>
       </c>
-      <c r="R176" t="inlineStr">
+      <c r="R176" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21053,6 +23896,46 @@
       <c r="T176" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U176" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V176" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W176" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Indian arm of global Randstad; no open API for India specifically. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X176" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y176" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z176" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA176" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB176" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21140,7 +24023,7 @@
       <c r="Q177" t="n">
         <v>0</v>
       </c>
-      <c r="R177" t="inlineStr">
+      <c r="R177" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21153,6 +24036,46 @@
       <c r="T177" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U177" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V177" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W177" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Indian arm of global Adecco; no public job feed. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X177" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y177" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z177" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA177" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB177" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21240,7 +24163,7 @@
       <c r="Q178" t="n">
         <v>0</v>
       </c>
-      <c r="R178" t="inlineStr">
+      <c r="R178" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21253,6 +24176,46 @@
       <c r="T178" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U178" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V178" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W178" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Indian arm of global ManpowerGroup; no public job feed. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X178" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y178" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z178" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA178" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB178" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21340,7 +24303,7 @@
       <c r="Q179" t="n">
         <v>0</v>
       </c>
-      <c r="R179" t="inlineStr">
+      <c r="R179" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21353,6 +24316,46 @@
       <c r="T179" t="inlineStr">
         <is>
           <t>Not applicable - no public feed</t>
+        </is>
+      </c>
+      <c r="U179" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V179" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W179" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Indian arm of global Kelly Services; no public job feed. See report Sec 16.4 (India).</t>
+        </is>
+      </c>
+      <c r="X179" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y179" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z179" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA179" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB179" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21440,9 +24443,9 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R180" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (varies per resource; not a single index)</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -21453,6 +24456,46 @@
       <c r="T180" t="inlineStr">
         <is>
           <t>Investigate - some resources have REST APIs, worth a per-resource review (Medium effort)</t>
+        </is>
+      </c>
+      <c r="U180" s="8" t="inlineStr">
+        <is>
+          <t>India (varies per individual OGD resource)</t>
+        </is>
+      </c>
+      <c r="V180" s="8" t="inlineStr">
+        <is>
+          <t>N/A - India-only government open-data platform</t>
+        </is>
+      </c>
+      <c r="W180" s="8" t="inlineStr">
+        <is>
+          <t>Not a single provider with one endpoint - it's a platform of many independent resources, some with REST APIs and some without; each candidate resource needs its own per-resource review before integration.</t>
+        </is>
+      </c>
+      <c r="X180" s="8" t="inlineStr">
+        <is>
+          <t>Investigate: review candidate employment-related resources on data.gov.in individually; where a resource exposes a REST API, treat it as a small New API integration (free key), otherwise as a Custom connector (bulk dataset ETL).</t>
+        </is>
+      </c>
+      <c r="Y180" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (varies per resource)</t>
+        </is>
+      </c>
+      <c r="Z180" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AA180" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB180" s="8" t="inlineStr">
+        <is>
+          <t>New API integration or Custom connector, decided per-resource after investigation</t>
         </is>
       </c>
     </row>
@@ -21540,7 +24583,7 @@
       <c r="Q181" t="n">
         <v>0</v>
       </c>
-      <c r="R181" t="inlineStr">
+      <c r="R181" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21553,6 +24596,46 @@
       <c r="T181" t="inlineStr">
         <is>
           <t>Low priority - state-level fragmentation kills ROI</t>
+        </is>
+      </c>
+      <c r="U181" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V181" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W181" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Uttar Pradesh state employment exchange portal; one of 28+ fragmented state systems with no common API. See report Sec 16.1/16.5 (India).</t>
+        </is>
+      </c>
+      <c r="X181" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y181" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z181" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA181" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB181" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21640,7 +24723,7 @@
       <c r="Q182" t="n">
         <v>0</v>
       </c>
-      <c r="R182" t="inlineStr">
+      <c r="R182" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21653,6 +24736,46 @@
       <c r="T182" t="inlineStr">
         <is>
           <t>Low priority - state-level fragmentation kills ROI</t>
+        </is>
+      </c>
+      <c r="U182" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V182" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W182" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Maharashtra state employment portal; one of 28+ fragmented state systems with no common API. See report Sec 16.1/16.5 (India).</t>
+        </is>
+      </c>
+      <c r="X182" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y182" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z182" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA182" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB182" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21740,7 +24863,7 @@
       <c r="Q183" t="n">
         <v>0</v>
       </c>
-      <c r="R183" t="inlineStr">
+      <c r="R183" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21753,6 +24876,46 @@
       <c r="T183" t="inlineStr">
         <is>
           <t>Low priority - state-level fragmentation kills ROI</t>
+        </is>
+      </c>
+      <c r="U183" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V183" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W183" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Madhya Pradesh state employment portal; one of 28+ fragmented state systems with no common API. See report Sec 16.1/16.5 (India).</t>
+        </is>
+      </c>
+      <c r="X183" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y183" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z183" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA183" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB183" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21840,7 +25003,7 @@
       <c r="Q184" t="n">
         <v>0</v>
       </c>
-      <c r="R184" t="inlineStr">
+      <c r="R184" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -21853,6 +25016,46 @@
       <c r="T184" t="inlineStr">
         <is>
           <t>Low priority - state-level fragmentation kills ROI</t>
+        </is>
+      </c>
+      <c r="U184" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="V184" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W184" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Telangana state employment portal; one of 28+ fragmented state systems with no common API. See report Sec 16.1/16.5 (India).</t>
+        </is>
+      </c>
+      <c r="X184" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y184" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z184" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA184" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB184" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -21940,9 +25143,9 @@
       <c r="Q185" t="n">
         <v>0</v>
       </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R185" s="8" t="inlineStr">
+        <is>
+          <t>10,000-50,000 (unverified, per existing Total Estimated Jobs Available)</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -21953,6 +25156,46 @@
       <c r="T185" t="inlineStr">
         <is>
           <t>Optional - low priority, unverified volume (Low effort)</t>
+        </is>
+      </c>
+      <c r="U185" s="8" t="inlineStr">
+        <is>
+          <t>United States / remote tech jobs</t>
+        </is>
+      </c>
+      <c r="V185" s="8" t="inlineStr">
+        <is>
+          <t>Remote-only tech niche; not broadly region-scoped</t>
+        </is>
+      </c>
+      <c r="W185" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; requires a free-tier token registration first.</t>
+        </is>
+      </c>
+      <c r="X185" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (Low effort) once a token is registered; low priority given unverified volume and overlap with existing US/remote coverage.</t>
+        </is>
+      </c>
+      <c r="Y185" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (unverified volume; likely modest)</t>
+        </is>
+      </c>
+      <c r="Z185" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA185" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB185" s="8" t="inlineStr">
+        <is>
+          <t>Authentication implementation (free-tier token) + New API integration</t>
         </is>
       </c>
     </row>
@@ -22040,9 +25283,9 @@
       <c r="Q186" t="n">
         <v>0</v>
       </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R186" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (large but not quantified; partner-gated)</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -22053,6 +25296,46 @@
       <c r="T186" t="inlineStr">
         <is>
           <t>Low priority - partner-gated, hard integration</t>
+        </is>
+      </c>
+      <c r="U186" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="V186" s="8" t="inlineStr">
+        <is>
+          <t>N/A - US-focused board; broader footprint not documented for the public-facing product</t>
+        </is>
+      </c>
+      <c r="W186" s="8" t="inlineStr">
+        <is>
+          <t>Partner approval is required before any integration work is possible; no self-serve API access exists.</t>
+        </is>
+      </c>
+      <c r="X186" s="8" t="inlineStr">
+        <is>
+          <t>Would require applying for partner status and negotiating access; not a pure engineering task.</t>
+        </is>
+      </c>
+      <c r="Y186" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (partner-gated)</t>
+        </is>
+      </c>
+      <c r="Z186" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA186" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB186" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (partner approval required)</t>
         </is>
       </c>
     </row>
@@ -22140,7 +25423,7 @@
       <c r="Q187" t="n">
         <v>0</v>
       </c>
-      <c r="R187" t="inlineStr">
+      <c r="R187" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22153,6 +25436,46 @@
       <c r="T187" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U187" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="V187" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W187" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; US niche (senior/executive) job board. See report Sec 10.2 (US).</t>
+        </is>
+      </c>
+      <c r="X187" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y187" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z187" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA187" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB187" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -22240,7 +25563,7 @@
       <c r="Q188" t="n">
         <v>0</v>
       </c>
-      <c r="R188" t="inlineStr">
+      <c r="R188" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22253,6 +25576,46 @@
       <c r="T188" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U188" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="V188" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W188" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; US tech-niche job board. See report Sec 10.2 (US).</t>
+        </is>
+      </c>
+      <c r="X188" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y188" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z188" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA188" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB188" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -22340,7 +25703,7 @@
       <c r="Q189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="inlineStr">
+      <c r="R189" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22353,6 +25716,46 @@
       <c r="T189" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U189" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="V189" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W189" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. No public API; US tech/startup job board. See report Sec 10.2 (US).</t>
+        </is>
+      </c>
+      <c r="X189" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y189" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z189" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA189" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB189" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -22440,9 +25843,9 @@
       <c r="Q190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R190" s="8" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -22453,6 +25856,46 @@
       <c r="T190" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U190" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom (health sector)</t>
+        </is>
+      </c>
+      <c r="V190" s="8" t="inlineStr">
+        <is>
+          <t>N/A - UK-only, sector-specific board</t>
+        </is>
+      </c>
+      <c r="W190" s="8" t="inlineStr">
+        <is>
+          <t>No documented public API for this board at all.</t>
+        </is>
+      </c>
+      <c r="X190" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration; would require a data-sharing agreement with NHS or scraping (not recommended).</t>
+        </is>
+      </c>
+      <c r="Y190" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without an API</t>
+        </is>
+      </c>
+      <c r="Z190" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA190" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB190" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -22540,9 +25983,9 @@
       <c r="Q191" t="n">
         <v>0</v>
       </c>
-      <c r="R191" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R191" s="8" t="inlineStr">
+        <is>
+          <t>N/A - no consumer read API</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -22553,6 +25996,46 @@
       <c r="T191" t="inlineStr">
         <is>
           <t>Not applicable - no consumer read API</t>
+        </is>
+      </c>
+      <c r="U191" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom (civil service)</t>
+        </is>
+      </c>
+      <c r="V191" s="8" t="inlineStr">
+        <is>
+          <t>N/A - UK-only, sector-specific board</t>
+        </is>
+      </c>
+      <c r="W191" s="8" t="inlineStr">
+        <is>
+          <t>Only an employer-posting feed exists; there is no consumer-facing read/search API to pull listings from.</t>
+        </is>
+      </c>
+      <c r="X191" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via a read-only aggregator model; the only documented feed serves posting, not reading.</t>
+        </is>
+      </c>
+      <c r="Y191" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable via a read API</t>
+        </is>
+      </c>
+      <c r="Z191" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA191" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB191" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API - posting-only feed exists, not a read/search API)</t>
         </is>
       </c>
     </row>
@@ -22640,9 +26123,9 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R192" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (CZ/SK; not quantified)</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -22653,6 +26136,46 @@
       <c r="T192" t="inlineStr">
         <is>
           <t>Low priority - partner-only, paid</t>
+        </is>
+      </c>
+      <c r="U192" s="8" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="V192" s="8" t="inlineStr">
+        <is>
+          <t>N/A - CZ-focused; Profesia (row 193) is the sister SK board under the same ownership</t>
+        </is>
+      </c>
+      <c r="W192" s="8" t="inlineStr">
+        <is>
+          <t>Partner-only paid access - no open API to build against.</t>
+        </is>
+      </c>
+      <c r="X192" s="8" t="inlineStr">
+        <is>
+          <t>Would require negotiating partner/paid access; low priority given thin CZ/SK volume relative to effort.</t>
+        </is>
+      </c>
+      <c r="Y192" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (partner-gated)</t>
+        </is>
+      </c>
+      <c r="Z192" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA192" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB192" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (partner approval required)</t>
         </is>
       </c>
     </row>
@@ -22740,9 +26263,9 @@
       <c r="Q193" t="n">
         <v>0</v>
       </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R193" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (CZ/SK; not quantified)</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -22753,6 +26276,46 @@
       <c r="T193" t="inlineStr">
         <is>
           <t>Low priority - partner-only, paid</t>
+        </is>
+      </c>
+      <c r="U193" s="8" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="V193" s="8" t="inlineStr">
+        <is>
+          <t>N/A - SK-focused; Jobs.cz (row 192) is the sister CZ board under the same ownership</t>
+        </is>
+      </c>
+      <c r="W193" s="8" t="inlineStr">
+        <is>
+          <t>Partner-only paid access - no open API to build against.</t>
+        </is>
+      </c>
+      <c r="X193" s="8" t="inlineStr">
+        <is>
+          <t>Would require negotiating partner/paid access; low priority given thin CZ/SK volume relative to effort.</t>
+        </is>
+      </c>
+      <c r="Y193" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (partner-gated)</t>
+        </is>
+      </c>
+      <c r="Z193" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AA193" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB193" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise onboarding (partner approval required)</t>
         </is>
       </c>
     </row>
@@ -22840,7 +26403,7 @@
       <c r="Q194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="inlineStr">
+      <c r="R194" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -22853,6 +26416,46 @@
       <c r="T194" t="inlineStr">
         <is>
           <t>Not applicable - no public API</t>
+        </is>
+      </c>
+      <c r="U194" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="V194" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not documented; irrelevant while no public API exists regardless of region</t>
+        </is>
+      </c>
+      <c r="W194" s="8" t="inlineStr">
+        <is>
+          <t>No public API exists at all - this is the blocking gap, not a query/region gap. Colombia's largest job board; no public API, scraping only. See report Sec 10.7 (LATAM).</t>
+        </is>
+      </c>
+      <c r="X194" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration. The only alternative route would be a licensed data partnership or scraping (not recommended per report); no amount of engineering substitutes for the missing API.</t>
+        </is>
+      </c>
+      <c r="Y194" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without a public API</t>
+        </is>
+      </c>
+      <c r="Z194" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA194" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB194" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>
@@ -22940,9 +26543,9 @@
       <c r="Q195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="R195" s="8" t="inlineStr">
+        <is>
+          <t>Small (not quantified, per existing Notes)</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -22953,6 +26556,46 @@
       <c r="T195" t="inlineStr">
         <is>
           <t>Optional - low priority, small volume (Low effort)</t>
+        </is>
+      </c>
+      <c r="U195" s="8" t="inlineStr">
+        <is>
+          <t>Remote-LATAM job board</t>
+        </is>
+      </c>
+      <c r="V195" s="8" t="inlineStr">
+        <is>
+          <t>Remote-only by nature; not region-scoped beyond that</t>
+        </is>
+      </c>
+      <c r="W195" s="8" t="inlineStr">
+        <is>
+          <t>No integration exists yet; otherwise a free API/RSS with no major auth barrier - the gap is simply that no connector has been written.</t>
+        </is>
+      </c>
+      <c r="X195" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (Low effort) - low priority given the report's noted small volume and overlap with existing remote feeds (Himalayas/RemoteOK/Jobicy).</t>
+        </is>
+      </c>
+      <c r="Y195" s="8" t="inlineStr">
+        <is>
+          <t>Unknown (low volume expected, per Notes)</t>
+        </is>
+      </c>
+      <c r="Z195" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AA195" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB195" s="8" t="inlineStr">
+        <is>
+          <t>New API integration (free API/RSS)</t>
         </is>
       </c>
     </row>
@@ -23040,9 +26683,9 @@
       <c r="Q196" t="n">
         <v>0</v>
       </c>
-      <c r="R196" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="R196" s="8" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -23053,6 +26696,46 @@
       <c r="T196" t="inlineStr">
         <is>
           <t>Not applicable - no documented API</t>
+        </is>
+      </c>
+      <c r="U196" s="8" t="inlineStr">
+        <is>
+          <t>Singapore (public sector)</t>
+        </is>
+      </c>
+      <c r="V196" s="8" t="inlineStr">
+        <is>
+          <t>N/A - Singapore-only, sector-specific portal</t>
+        </is>
+      </c>
+      <c r="W196" s="8" t="inlineStr">
+        <is>
+          <t>No documented public API for this portal at all.</t>
+        </is>
+      </c>
+      <c r="X196" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable via API integration; low priority given small public-sector volume regardless.</t>
+        </is>
+      </c>
+      <c r="Y196" s="8" t="inlineStr">
+        <is>
+          <t>Unknown - not integrable without an API</t>
+        </is>
+      </c>
+      <c r="Z196" s="8" t="inlineStr">
+        <is>
+          <t>N/A (no public API - not applicable)</t>
+        </is>
+      </c>
+      <c r="AA196" s="8" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="AB196" s="8" t="inlineStr">
+        <is>
+          <t>Not feasible (No Public API)</t>
         </is>
       </c>
     </row>

--- a/job_api_catalog.xlsx
+++ b/job_api_catalog.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="API Catalog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Integration Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Schema Definitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema Definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$U$362</definedName>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (public labor exchange aggregating state job banks and private employer postings via the National Labor Exchange)</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset-style path parameters: {startRecord}/{pageSize} (e.g. /v2/jobsearch/{userId}/{keyword}/{location}/{radius}/{sortColumns}/{sortOrder}/{startRecord}/{pageSize}/{days}); all parameters required on every request</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (aggregates career-site and ATS job postings across all sectors)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset/limit: limit param (1-1,000 per request, default 100) + offset param; increase offset by limit each call until a response returns fewer rows than limit</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (broad multi-source job postings and professional data used for HR tech, sales intelligence, and market research)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cursor-based: after parameter (numeric ID cursor, or score+timestamp+ID cursor when sorting by score) plus items_per_page (max 1,000/page); response includes x-next-page-after, x-total-pages, x-total-results headers</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (national job board covering all occupations under Canada's National Occupational Classification)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (horizontal job search aggregator spanning all employment categories)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>For employers submitting vacancies: SFTP upload using username/password credentials, per DWP's official 'Find a Job' Bulk Upload Specification (XML files sent to an SFTP server with assigned credentials). No confirmed public read/search API exists for third parties to consume listings.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (UK government job service covering all sectors and skill levels)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (job search engine aggregating listings across all industries and career levels)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (French national public employment service covering all business sectors)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset-style via range parameter (e.g. range=0-149, default 0-149); max 150 results/request, max range endpoint index 1149 (up to 1150 total results per query); rate-limited to 3 req/sec; larger result sets require narrowing with minCreationDate/maxCreationDate</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (pan-EU job mobility portal spanning all sectors and occupations)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (horizontal job search aggregator spanning all employment categories)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (Government of India career/employment portal covering 52 sectors)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (India's largest horizontal job portal spanning sales, IT, finance, engineering, and more)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (broad job portal spanning IT, finance, sales, HR, marketing, and more)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue-collar/grey-collar and vocational jobs (delivery, security, domestic work, telecalling/BPO, skilled trades)</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (professional network job platform spanning 20 root industries / 434 sub-industries)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (horizontal job search engine spanning all sectors)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (aggregates career-site and ATS job postings across all sectors)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset/limit: limit param (1-1,000 per request, default 100) + offset param; increase offset by limit each call until a response returns fewer rows than limit</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (broad multi-source job postings and professional data used for HR tech, sales intelligence, and market research)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cursor-based: after parameter (numeric ID cursor, or score+timestamp+ID cursor when sorting by score) plus items_per_page (max 1,000/page); response includes x-next-page-after, x-total-pages, x-total-results headers</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (job-data aggregator/scraper covering multiple job boards and industries)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cursor-based: size param (10-100/request, default 100) + cursor param; response returns next_cursor to pass into the next request; continue until response returns status: no_data</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (aggregates Google for Jobs and open-web listings across all publishers/sectors)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (scrapes Google Jobs search results across all job categories)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (ATS/recruitment CRM for staffing agencies and corporate HR teams of any size or industry)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (ATS/HR platform used across 21+ industries incl. education, manufacturing, professional services, nonprofits)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (enterprise HRMS/ATS software vendor; client base spans retail, aviation/FMCG (Adani), F&amp;B (Starbucks), conglomerates (Mahindra), tech (Swiggy, Tokopedia) with no single-sector focus)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (HR &amp; payroll software marketed to IT/services, manufacturing, education, financial services, retail, automotive and other sectors)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (cloud HRMS/payroll serving IT/SaaS, manufacturing, healthcare, banking, hospitality, education, retail per greythr.com)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (Singapore government career portal covering all sectors, incl. logistics, healthcare, tourism/hospitality, green infrastructure)</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (broad consumer employment marketplace across APAC; official merger press release describes it as a general employment marketplace, not niche)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (horizontal job search aggregator spanning all employment categories)</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -14148,57 +14148,57 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>Free tier + Paid (metered)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Likely free/low-cost (unverified)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Likely yes</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Technology/Startups (curated tech &amp; startup jobs across Latin America: programming, data science, UX/design, DevOps/SysAdmin, mobile, ML/AI, product, tech sales/marketing)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Moderate (est. 5,000-20,000)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Likely free/low-cost (unverified)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Likely yes</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Unknown (advertised, not independently verified)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>LATAM tech-focused job board; one of the few LATAM boards with an advertised public API (unverified). See report Sec 16 (LATAM).</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t>Moderate (est. 5,000-20,000)</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Unknown (advertised, not independently verified)</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>LATAM tech-focused job board; one of the few LATAM boards with an advertised public API (unverified). See report Sec 16 (LATAM).</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Moderate (est. 5,000-20,000)</t>
-        </is>
-      </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page/per_page query params; page default 1, per_page default and max 100</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/all-industries (horizontal job search aggregator spanning all employment categories)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (official job search engine of the Canada's Top 100 Employers project; indexes direct-employer jobs across all sectors, no niche)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid/Enterprise job-insertion API only (not job aggregation); pricing is customized by company size and not publicly published - custom quote required</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14688,29 +14688,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
+          <t>No direct fee - the Publisher/backfill program (XML feed or self-serve API) is revenue-share/CPC (cost-per-click) based; publishers earn per click on displayed jobs rather than paying to access the feed. Exact CPC rates are not published and require contacting Talent.com's partner team.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>General/All-industries (broad global job search aggregator; no sector specialization stated)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>N/A - no public API</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>N/A - no public API</t>
-        </is>
-      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>No</t>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>40 million+ jobs (global figure stated on talent.com homepage)</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API; the wowjobs.ca domain now 301-redirects to SimplyHired.ca, indicating WowJobs no longer operates as an independent job board</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14912,42 +14912,42 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
+          <t>General/All-industries (labor market intelligence platform; job postings scraped from 220,000+ sites worldwide and classified across all NAICS industries, not a niche vertical)</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Default 10 requests/sec per client; adjustable via auth claims (e.g. postings:us:rate-limit:100/1, or unlimited on enterprise contracts); OAuth bearer tokens required, valid 1 hour</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Commercial/paid API; report explicitly recommends against integrating - out of scope for a free-source project. See report Sec 5 (Canada).</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Not Recommended</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Commercial/paid API; report explicitly recommends against integrating - out of scope for a free-source project. See report Sec 5 (Canada).</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Not Recommended</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset/limit-style (limit param, max 1,000/page; page param also supported per API changelog); OAuth bearer token required (1-hour validity)</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Enterprise/partner-only; pricing not published. Access is via a formal 'Feed Questionnaire' application through the StepStone Group API portal, which explicitly lists Totaljobs.com among its integrated job boards.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Enterprise/partner-only; pricing not published. Both the Job Search API and Job View API are 'not provided as standard' - access requires applying to CV-Library's Partner team.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Enterprise/partner-only; pricing not published. Access is via a formal 'Feed Questionnaire' application through the StepStone Group API portal, which explicitly lists Jobsite.co.uk among its integrated job boards.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries ("find any type of job, in any industry" per jobsite.co.uk)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>280,000+ (UK-only platform, per jobsite.co.uk)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>280,000+ live job adverts (per jobsite.co.uk About Us page)</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Enterprise/partner-only; pricing not published. Access is via a formal 'Feed Questionnaire' application through the StepStone Group API portal, which explicitly lists CWJobs.co.uk among its integrated job boards.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -15340,12 +15340,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Technology/IT (specialist tech and IT recruitment board, per cwjobs.co.uk)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>12,000+ (UK-only platform, per cwjobs.co.uk)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>12,000+ jobs (per cwjobs.co.uk About Us page)</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Official StepStone Belgium price list (PDF, 2019) shows a JobFeed feed-integration one-time setup fee of €1,000 (feed itself is customer-specific/individually scoped thereafter, no public recurring fee listed); standalone job-ad posting products range €999–€1,899; CV database access €399–€14,999 depending on duration/number of users. StepStone's official German JobFeed brochure (api.stepstone.com) confirms JobFeed setup is customer-specific and individually quoted, with extra technical work invoiced separately — no public flat API rate is published. Pricing may be dated (2019 documents) so treat as indicative, not current.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not publicly disclosed - enterprise/partner pricing only; requires direct contact with New Work SE (Xing) (confirmed no self-service API pricing page on official site)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No public price list found. Official Partner Program page (corporate.jobrapido.com) confirms a commission/revenue-share model — partners "earn commissions" with "competitive commissions" and real-time revenue dashboards — but exact rates/percentages are not publicly disclosed; terms are negotiated after filling in a form and booking a demo.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (broad job search aggregator matching jobseekers across traditional job boards and employer sites; no niche stated)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -15753,12 +15753,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/All-industries (multi-sector recruitment/media platform; no niche industry stated on official About Us page)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15860,12 +15860,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries (horizontal LATAM job board)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -15967,12 +15967,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -16089,13 +16089,11 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+          <t>General / all-industries (horizontal Mexico job board; report highlights growth in social sciences/humanities, sports-health-beauty, and communication/creativity categories)</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>137925</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -16119,7 +16117,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>137,925 active vacancies ("vacantes activas en occ.com.mx", as of Oct 18, 2024); lifetime total of 17.5+ million vacancies published over 27 years</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -16181,12 +16179,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -16288,12 +16286,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -16410,17 +16408,15 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+          <t>General / multi-industry remote jobs (categories include programming, design, marketing, sales, writing, data science, devops, product, customer support, finance, HR, legal)</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>800</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No signup/API key required; 'reasonable use' policy with no hard rate cap stated; max 50 jobs/request; contact provider (ryan@remotejobs.org) for higher volume</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -16440,12 +16436,12 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>800+ jobs (API pagination sample shows total: 808)</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset/limit: limit param (min 1, max 50, default 20) + offset param (default 0, jobs to skip)</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -16517,42 +16513,42 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
+          <t>General / all-industries enterprise HCM software (used across IT services, GCCs, banking, manufacturing, healthcare, finance)</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Unknown (per-tenant; no aggregate index)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Partial — Workday does publish official API documentation, but the documentation entry point (community.workday.com/api) redirects to a Workday Community page that returned HTTP 401 Unauthorized when accessed without an authenticated Workday Community/customer login. No official Workday page could be found that documents the public per-tenant career-site JSON (CXS) endpoint referenced in this row's notes — that interface is not part of Workday's publicly documented API surface.</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Per-tenant career-site JSON endpoints used by many large Indian enterprises; high enterprise-India value but meaningful per-tenant integration effort - the notable gap in this project's ATS coverage. See report Sec 16.3 (India).</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t>Unknown (per-tenant; no aggregate index)</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Per-tenant career-site JSON endpoints used by many large Indian enterprises; high enterprise-India value but meaningful per-tenant integration effort - the notable gap in this project's ATS coverage. See report Sec 16.3 (India).</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Unknown (per-tenant; no aggregate index)</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Page/Count via Response_Filter on Get_Job_Requisitions: Count (min 1, max 999, default 100), Page (default 1; Page param requires also setting As_Of_Entry_Date for a consistent result set across paged requests); response returns Total_Results/Total_Pages/Page_Results</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -16609,12 +16605,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Restricted - developer.ceipal.com portal requires sign-in/account approval (confirmed: restricted-access pages on official domain); tied to the CEIPAL ATS platform, not an open public job-data API</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not publicly disclosed - Ceipal does not publish API/product pricing (confirmed via official ceipal.com/pricing page, which offers no listed prices and requires booking a demo); custom quote-based</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -16624,7 +16620,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Staffing &amp; recruiting industry (general/IT/healthcare staffing verticals)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -16634,12 +16630,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes — CEIPAL publishes an official public Developer Portal at developer.ceipal.com, with indexed pages titled "CEIPAL ATS API V2 Documentation | Developer Portal," "Ceipal ATS v1 API Reference," an API Explorer, and a Changelog. Direct fetch was blocked by bot protection (HTTP 403), but the portal's existence and content are confirmed via search-engine indexing of the official domain.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -16731,7 +16727,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Recruitment &amp; staffing agencies (general, global, including executive search)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -16746,7 +16742,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes — official public Help Center article describes the API and links to full documentation at docs.recruitcrm.io, viewable without login. Confirms Bearer-token authentication and that Open API access is limited to Business-plan-or-higher account owners.</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -16838,7 +16834,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries SMB and mid-market HR software</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -16853,7 +16849,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes — official public documentation at documentation.bamboohr.com/docs/getting-started, viewable without login, describing both OAuth (for apps serving multiple customers) and API-key/HTTP Basic authentication (for direct customer integrations).</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -16930,12 +16926,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -16945,7 +16941,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries consumer job board (IT, marketing, finance, medical, blue-collar, government, etc.)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17037,12 +17033,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -17144,12 +17140,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -17159,7 +17155,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue-collar / grey-collar jobs</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -17251,12 +17247,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -17266,7 +17262,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Technology / startup jobs</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -17358,12 +17354,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -17373,7 +17369,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Technology / tech professional jobs (startups and MNCs)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -17465,12 +17461,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -17480,7 +17476,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Technology / IT jobs (India's IT-only job portal)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -17572,12 +17568,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -17587,7 +17583,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Management / MBA jobs (banking &amp; finance, consulting, sales &amp; marketing, HR, IT, operations)</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -17694,7 +17690,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries entry-level and fresher jobs (engineering, IT, government, banking, teaching, defence, etc.)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -17786,12 +17782,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -17801,7 +17797,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries internships and entry-level jobs (200+ profiles/domains)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -17893,12 +17889,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -17908,7 +17904,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Education / early-career talent engagement (students, freshers, 0-5 yrs professionals; competitions, hackathons, internships, jobs)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -18000,12 +17996,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -18015,7 +18011,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech/startup jobs (general startup ecosystem)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -18122,7 +18118,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech/startup jobs (India)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -18214,12 +18210,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API (HackerEarth publishes a separate developer API for code evaluation/recruiter test-invites, but no public API for the Jobs listings board)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -18229,7 +18225,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech/developer jobs (software engineering)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -18336,7 +18332,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General/campus recruitment (all industries, entry-level/fresher hiring across 400+ colleges)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -18351,7 +18347,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -18428,12 +18424,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -18443,13 +18439,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+          <t>General staffing, blue-collar and multi-industry workforce solutions</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>23082</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -18473,7 +18467,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>23,082+ active job vacancies (live count on official site)</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -18535,12 +18529,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -18550,7 +18544,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General staffing, multi-industry workforce/asset management and IT services</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -18642,12 +18636,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -18657,13 +18651,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+          <t>General staffing, multi-industry recruitment</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>1394</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -18687,7 +18679,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1,394 jobs (live count on official site)</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -18749,12 +18741,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -18764,7 +18756,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General staffing, multi-industry recruitment</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -18856,12 +18848,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -18871,7 +18863,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General staffing across IT and Non-IT sectors (workforce management)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -18963,12 +18955,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public feed</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -18978,7 +18970,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General staffing, multi-industry (accounting/finance, engineering, manufacturing, technology, etc.)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -19085,7 +19077,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government/general (open datasets spanning 33 sectors, not jobs-specific)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -19177,22 +19169,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API (portal uses role-based login for Job Seeker/Institution/Employer/Department users, not third-party API auth)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government/general employment exchange (private, government, and outsourced jobs across all sectors)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -19207,7 +19199,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -19227,7 +19219,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -19284,22 +19276,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free (public government portal; no paid API product)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government/general, multi-sector (skilled/semi-skilled/unskilled labor across engineering, logistics, textiles, manufacturing, pharma, etc.)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -19314,7 +19306,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -19334,7 +19326,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -19391,22 +19383,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free (public government portal; no paid API product)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government/general employment exchange (all sectors, statewide job-seeker registry)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -19421,7 +19413,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -19441,7 +19433,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -19498,22 +19490,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free (public government portal; no paid API product)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government/general employment exchange (all sectors)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -19528,7 +19520,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -19548,7 +19540,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -19635,7 +19627,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -19742,7 +19734,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -19762,7 +19754,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - Partner Job API is a single-endpoint write API (api.ziprecruiter.com/partner/v0/job) for creating/updating/closing job listings on ZipRecruiter's network; not a paginated read/search endpoint</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -19819,12 +19811,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -19834,7 +19826,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Professional/executive jobs (senior roles, $100K+ salary skew, general industries)</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19926,12 +19918,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -19941,7 +19933,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech/IT (information technology and engineering professionals)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -20033,12 +20025,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20048,7 +20040,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech/startup jobs</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -20140,12 +20132,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No published fee; NHS Jobs Self-Serve API and ATS API exist but access is restricted to organisations meeting eligibility criteria (roles must be health/NHS-associated) via enquiry to NHS Jobs support</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20155,7 +20147,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Healthcare (NHS / public health service)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20247,12 +20239,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no consumer-facing public API; employer-side job posting feed only)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public consumer API</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20262,7 +20254,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government / Public Sector (general, cross-department civil service roles)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -20369,42 +20361,42 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
+          <t>General / all-industries (Czech Republic; skews toward specialist and university-educated professional roles)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Medium (CZ/SK; not quantified)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Czech Republic job board; partner-only paid access, no open API. See report Sec 10.4 (Europe).</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Enterprise Only</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t>Medium (CZ/SK; not quantified)</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Czech Republic job board; partner-only paid access, no open API. See report Sec 10.4 (Europe).</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>Enterprise Only</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>Medium (CZ/SK; not quantified)</t>
-        </is>
-      </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - write-only XML feed import for employers (postings pushed to LMC's g2.lmc.cz/import/... endpoint via Teamio/LMC integration); no public job-listings read/search API to paginate</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -20476,42 +20468,42 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
+          <t>General / all-industries (Slovakia's largest general job portal)</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Medium (CZ/SK; not quantified)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Slovakia job board; partner-only paid access, no open API. See report Sec 10.4 (Europe).</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Enterprise Only</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t>Medium (CZ/SK; not quantified)</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Slovakia job board; partner-only paid access, no open API. See report Sec 10.4 (Europe).</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>Enterprise Only</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Medium (CZ/SK; not quantified)</t>
-        </is>
-      </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - write/import API for employers to submit job listings to Profesia.sk (token-based bulk feed import); no public job-listings read/search API to paginate</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -20568,12 +20560,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20583,7 +20575,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries (broad multi-sector Colombian job board)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -20690,7 +20682,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>General / all-industries remote jobs (broad categories: dev, design, marketing, sales, customer support, admin, etc., with a knowledge-work/tech skew)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -20705,7 +20697,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -20782,12 +20774,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -20797,7 +20789,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Government / Public Sector (Singapore Public Service - all Ministries and Statutory Boards)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -20934,7 +20926,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>~90,000 job vacancies published monthly on the Gupy R&amp;S platform (official figure)</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -20959,7 +20951,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -20969,7 +20961,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -21021,32 +21013,32 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Yes - forbusiness.vagas.com.br/developers lists a Job Feed API, Job Publication API, and candidate-export API, with Apiary-hosted reference docs</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>One of Brazil's oldest large job boards/ATS (Vagas.com). Confirmed real developer portal, but access is scoped to each business customer's own postings/candidates, not an open market-wide feed. | Access detail: Client/Partner (existing Vagas for Business customers)</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Yes - forbusiness.vagas.com.br/developers lists a Job Feed API, Job Publication API, and candidate-export API, with Apiary-hosted reference docs</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>One of Brazil's oldest large job boards/ATS (Vagas.com). Confirmed real developer portal, but access is scoped to each business customer's own postings/candidates, not an open market-wide feed. | Access detail: Client/Partner (existing Vagas for Business customers)</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -21061,22 +21053,22 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
@@ -21128,7 +21120,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -21153,7 +21145,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -21168,22 +21160,22 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
@@ -21220,7 +21212,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes - dados.gov.br CKAN API requires authentication (direct call to /api/3/action/package_show for this dataset returned HTTP 401 without credentials)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -21235,7 +21227,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - data-sharing suspended since 3 Oct 2022 under Resolucao CODEFAT No. 956/2022, pending LGPD compliance updates; no active service to rate-limit</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -21260,7 +21252,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - data-sharing suspended since 3 Oct 2022 under Resolucao CODEFAT No. 956/2022 (suspending prior Resolutions 826/2019 and 844/2019) pending LGPD (Lei 13.709/2018) compliance updates; no active API to paginate</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -21275,12 +21267,12 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - service suspended (see Pagination note)</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - service suspended (see Pagination note)</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -21327,7 +21319,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No - datos.gob.mx CKAN API is publicly accessible without authentication (verified via direct call to /api/3/action/package_show, HTTP 200, dataset flagged private:false)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -21424,7 +21416,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -21434,7 +21426,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes - registered users log in with RUN/passport or ClaveÚnica to use the portal. Employers can additionally request an API service ('Servicio API' for JobOfferings/JobPosting) whose access credentials/token are issued through the company profile after a request - this is a real but employer-account-gated API, not a fully open public API.</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -21449,7 +21441,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -21531,7 +21523,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -21541,7 +21533,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Registered user account required (DNI, email, mobile phone) to log in via web browser; no API or programmatic access documented.</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -21556,7 +21548,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -21638,32 +21630,32 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
+          <t>Free tier + Paid (metered)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Free tier: up to 3 free listings/month, 30-day publication, first 5 applicant CVs unlocked (48h review before publishing). Paid tiers (Classic/Gold/Platinum): preferential placement and unlimited CV access, plus a 'Select' pay-per-contact model.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Employer account registration required (name, email, password, CUIT/tax ID, company data); no public API.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>General / cross-industry</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>General / cross-industry</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -21745,7 +21737,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (no public API)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -21755,7 +21747,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Registered user login required (document ID number + password, selecting 'Company' or 'Person' profile type) to search/view individual vacancies; no public API for vacancy data (Colombia's Socrata open-data API only exposes aggregate registration statistics, not live listings).</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -21770,7 +21762,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -21795,7 +21787,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -21810,22 +21802,22 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
@@ -21857,12 +21849,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -21902,7 +21894,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -21964,7 +21956,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free unlimited job posting (basic tier, no credit card). Paid upgrades: Spotlight (24hr homepage boost), Boost 3/10/30 packages, Pro monthly/annual subscription, and Resume Search contact packs at $35/month; paid single-post pricing starts around $30.19.</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -22004,12 +21996,12 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>150K jobs successfully posted (cumulative figure since 2004, per official site stats banner)</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -22076,7 +22068,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Registered user account required (name, CNIC, mobile number, email, password) via njp.gov.pk/register and login.php to search/apply for jobs; no API or developer access documented.</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -22091,7 +22083,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -22116,7 +22108,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -22183,7 +22175,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Registered user account required (phone number + OTP verification, then application form) via jobs.gov.pk/jobseeker/account/register and account/login; no API or developer access documented.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -22198,7 +22190,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -22223,7 +22215,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -22285,12 +22277,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Local employer packages: Basic TK 3,098, Stand-out TK 4,515, Stand-out Premium TK 6,195 (VAT incl., 30-day listing). Foreign employer packages: Basic $55, Stand-out $80, Stand-out Premium $105.</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Employer/recruiter account login required ('Sign In to Bdjobs Recruiter' at recruiter.bdjobs.com); no public API for job data.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -22305,7 +22297,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -22330,7 +22322,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -22397,47 +22389,47 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
+          <t>N/A - no public API</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Public sector / government employment</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Public sector / government employment</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Identified in search results as Bangladesh's National Government Job Portal (jobs.gov.bd); direct fetch of the site returned HTTP 403 (likely bot-blocking), so page content could not be directly verified, but the domain and its description as the official national portal are corroborated by multiple independent search results. No API or developer access mentioned in any available description. A separate 'Smart Job' portal at smartjob.portal.gov.bd also appears to be an official national portal - the two may be related or successive versions; this is unconfirmed.</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Identified in search results as Bangladesh's National Government Job Portal (jobs.gov.bd); direct fetch of the site returned HTTP 403 (likely bot-blocking), so page content could not be directly verified, but the domain and its description as the official national portal are corroborated by multiple independent search results. No API or developer access mentioned in any available description. A separate 'Smart Job' portal at smartjob.portal.gov.bd also appears to be an official national portal - the two may be related or successive versions; this is unconfirmed.</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -22519,7 +22511,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -22544,7 +22536,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -22606,12 +22598,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Rs. 6,400 per vacancy (14-day duration); US$35 per vacancy for international clients (incl. bank charges). Multi-vacancy packages range LKR 12,700 (2 vacancies) to LKR 67,100 (20 vacancies).</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Annual subscription/registration required for employers, arranged via direct contact with sales (ads@topjobs.lk) rather than self-service signup; no public API.</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -22626,7 +22618,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -22651,7 +22643,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -22713,52 +22705,52 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
+          <t>CV-based pricing (charged per CVs received, not per job ad): 5,000 LKR+VAT for 50 CVs up to 32,000 LKR+VAT for an unlimited monthly CV package; packages (except unlimited monthly) do not expire.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Recruiter account login required ('Recruiter Login' at /recruiter/account) to post jobs; no public API.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>General / all industries</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Unknown - claims recruitment relationships with 10,000+ organizations</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Sri Lankan job portal (relaunched with a new version in 2024) offering CV-less applications, timed tests, and video job ads. No API, developer portal, or programmatic-access documentation found on the site or in press coverage.</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>General / all industries</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Unknown - claims recruitment relationships with 10,000+ organizations</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Sri Lankan job portal (relaunched with a new version in 2024) offering CV-less applications, timed tests, and video job ads. No API, developer portal, or programmatic-access documentation found on the site or in press coverage.</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -22825,47 +22817,47 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
+          <t>No login required to browse publicly posted vacancy/gazette notices on psc.gov.lk; no API or developer access documented.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Public sector / government employment (civil service appointments, gazette vacancies)</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Unknown - publishes appointments, gazette notices, and vacancy announcements rather than a continuous large job feed</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Official constitutional body (established 1946) overseeing Sri Lanka's public service appointments; publishes vacancy/gazette announcements on psc.gov.lk plus provincial PSC sites. No API or developer access mentioned. Numerous unofficial third-party aggregator sites republish these notices but are not official sources.</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Public sector / government employment (civil service appointments, gazette vacancies)</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Unknown - publishes appointments, gazette notices, and vacancy announcements rather than a continuous large job feed</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Official constitutional body (established 1946) overseeing Sri Lanka's public service appointments; publishes vacancy/gazette announcements on psc.gov.lk plus provincial PSC sites. No API or developer access mentioned. Numerous unofficial third-party aggregator sites republish these notices but are not official sources.</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -22932,7 +22924,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not self-service - access is restricted to job portals that sign a formal MoU with Kemnaker. Confirmed via official Kemnaker press release that vacancy data sync between Karirhub and integrated partners (HiredToday, Toploker, Redy, Glints) uses API technology, but no publicly documented API key/OAuth mechanism exists for outside developers.</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -22972,7 +22964,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -22992,17 +22984,17 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -23029,57 +23021,57 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>N/A - no public API (employer job postings are paid via Midtrans payment processing; no API-specific pricing published)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Employer login/registration required (account with password, password-reset flow present); job postings are purchased via Midtrans payment processing. No public API documented.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>General (all industries)</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>One of Indonesia's oldest career portals (est. 1999), owned by EMTEK Group, ~1.3M monthly visits and 500+ employer partners. No public API, developer portal, or documentation could be found.</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>General (all industries)</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>One of Indonesia's oldest career portals (est. 1999), owned by EMTEK Group, ~1.3M monthly visits and 500+ employer partners. No public API, developer portal, or documentation could be found.</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -23099,17 +23091,17 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -23146,7 +23138,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No authentication required to browse/search job vacancies (public); free account registration is required for jobseekers to apply/receive matches and for employers/agencies to post jobs. No public API found on the official site.</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -23161,7 +23153,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -23186,7 +23178,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -23206,17 +23198,17 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
@@ -23243,57 +23235,57 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Free for employers to post; API/data-licensing pricing unknown</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>N/A - no public API</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>General, with strong tech/BPO presence</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Free for employers to post; API/data-licensing pricing unknown</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>AI/chat-first career platform (bossjob.ph) positioned as a leading Philippines hiring platform, also operating regionally (bossjob.com) across Southeast Asia. No public API or developer documentation found; employer FAQ and help center describe only the web/app posting flow.</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>General, with strong tech/BPO presence</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>AI/chat-first career platform (bossjob.ph) positioned as a leading Philippines hiring platform, also operating regionally (bossjob.com) across Southeast Asia. No public API or developer documentation found; employer FAQ and help center describe only the web/app posting flow.</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -23313,17 +23305,17 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
@@ -23400,7 +23392,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - OAuth2 JSON API (api.vietnamworks.com/api/rest/v1) only supports Post Job and Get Application (from an employer's own postings) flows; not a job-listings search/read API, so no aggregatable pagination applies</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -23415,7 +23407,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A (see Pagination note)</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -23457,7 +23449,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -23467,7 +23459,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes - API key (Access Token). TopCV's paid 'Top Developer API' service (data sync with recruitment/HRIS systems) requires an Access Token generated from the employer account's API connection settings on TopCV.</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -23482,7 +23474,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -23507,7 +23499,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -23527,17 +23519,17 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
@@ -23564,57 +23556,57 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Job seekers pay nothing for basic services; employers must purchase paid service packages ('gói dịch vụ có thu phí') to post jobs - specific rates not published on the official operating-rules page.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Yes - electronic identity verification. Employers must be electronically identified/verified by submitting required information and documents to CareerLink.vn before a job posting is activated.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>General (all industries)</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Unknown - reports 1,000+ new jobs posted daily</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Established Ho Chi Minh City-based job board (careerlink.vn) with nearly 20 years of operation and 1,000+ daily new job postings. No public API, developer portal, or documentation was found in this research; the company's GitHub org (careerlinkvn) shows internal tooling but no public job-data API.</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>General (all industries)</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Unknown - reports 1,000+ new jobs posted daily</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Established Ho Chi Minh City-based job board (careerlink.vn) with nearly 20 years of operation and 1,000+ daily new job postings. No public API, developer portal, or documentation was found in this research; the company's GitHub org (careerlinkvn) shows internal tooling but no public job-data API.</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -23634,17 +23626,17 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -23671,17 +23663,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Job posting is quote/rate-card based ('อัตราโฆษณา' advertising rates, with a downloadable rate file); employers request a quote via sale@jobthai.com rather than self-service free posting.</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -23696,7 +23688,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -23721,7 +23713,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -23741,17 +23733,17 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
@@ -23788,7 +23780,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public API</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -23803,7 +23795,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -23828,7 +23820,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -23848,17 +23840,17 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
@@ -23935,7 +23927,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -24042,7 +24034,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -24149,7 +24141,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -24216,47 +24208,47 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
+          <t>N/A - no public API</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>UAE federal government employment</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Unknown - likely small (federal government roles only)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>UAE's Ministry of Human Resources &amp; Emiratisation (MOHRE, mohre.gov.ae) is the verified real labor ministry; UAE federal government job vacancies are published via the iRecruitment portal referenced on u.ae. No API or developer documentation was discoverable for either MOHRE or iRecruitment.</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>UAE federal government employment</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Unknown - likely small (federal government roles only)</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>UAE's Ministry of Human Resources &amp; Emiratisation (MOHRE, mohre.gov.ae) is the verified real labor ministry; UAE federal government job vacancies are published via the iRecruitment portal referenced on u.ae. No API or developer documentation was discoverable for either MOHRE or iRecruitment.</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -24276,7 +24268,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -24338,7 +24330,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -24363,7 +24355,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -24383,7 +24375,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -24470,7 +24462,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -24577,7 +24569,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -24592,12 +24584,12 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -24659,7 +24651,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -24684,7 +24676,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -24704,7 +24696,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -24791,7 +24783,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -24898,7 +24890,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -24980,32 +24972,32 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>ESSA (essa.labour.gov.za), run by South Africa's Department of Employment and Labour, is a verified real government employment-matching platform. No public API or developer documentation was discoverable; the department also separately publishes its own internal vacancy circular for public-service jobs. | Access detail: Free government employment portal; no public read API</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>ESSA (essa.labour.gov.za), run by South Africa's Department of Employment and Labour, is a verified real government employment-matching platform. No public API or developer documentation was discoverable; the department also separately publishes its own internal vacancy circular for public-service jobs. | Access detail: Free government employment portal; no public read API</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -25025,7 +25017,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -25112,7 +25104,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -25127,12 +25119,12 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -25179,7 +25171,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes for the ATS/job-distribution API - an API credential is issued per account by MyJobMag's account manager after activation (custom, per-account terms). MyJobMag's public XML/RSS job feeds require no authentication.</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -25219,7 +25211,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -25286,47 +25278,47 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
+          <t>Not applicable - no public API found on the official site (nde.gov.ng); no API/developer documentation section exists.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Nigeria national employment/skills-acquisition programs</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Unknown - primarily a skills-training/job-creation program registry rather than an open vacancy board</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>The National Directorate of Employment (nde.gov.ng), established 1986 under Nigeria's Federal Ministry of Labour &amp; Employment, is a verified real government body running programs (e.g. Renewed Hope Employment Initiative, B-NOAS) via a registration portal (nderegistrationportal.ng). No public API or developer documentation was discoverable, and the portal is oriented around program registration rather than a searchable job feed.</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Nigeria national employment/skills-acquisition programs</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Unknown - primarily a skills-training/job-creation program registry rather than an open vacancy board</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>The National Directorate of Employment (nde.gov.ng), established 1986 under Nigeria's Federal Ministry of Labour &amp; Employment, is a verified real government body running programs (e.g. Renewed Hope Employment Initiative, B-NOAS) via a registration portal (nderegistrationportal.ng). No public API or developer documentation was discoverable, and the portal is oriented around program registration rather than a searchable job feed.</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -25346,7 +25338,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -25433,7 +25425,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -25448,12 +25440,12 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -25515,32 +25507,32 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>The National Employment Authority Integrated Management System (NEAIMS, neaims.go.ke), run by Kenya's National Employment Authority (nea.go.ke) with ILO support, is a verified real government platform matching jobseekers, employers, and private employment agencies for both local and overseas opportunities. No public API or developer documentation was discoverable. | Access detail: Free government employment platform; no public read API</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>The National Employment Authority Integrated Management System (NEAIMS, neaims.go.ke), run by Kenya's National Employment Authority (nea.go.ke) with ILO support, is a verified real government platform matching jobseekers, employers, and private employment agencies for both local and overseas opportunities. No public API or developer documentation was discoverable. | Access detail: Free government employment platform; no public read API</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -25560,7 +25552,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -25647,7 +25639,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -25754,7 +25746,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -25821,47 +25813,47 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
+          <t>N/A - no public API</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Egypt national labor/manpower administration and jobseeker registration</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Egypt national labor/manpower administration and jobseeker registration</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>N/A - no public read API</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Egypt's Ministry of Labour (renamed from Ministry of Manpower in 2023; labour.gov.eg / manpower.gov.eg) is a verified real government ministry that maintains an electronic database for jobseekers and runs online registration campaigns (e.g. for expatriate workers). No public API or developer documentation was discoverable.</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>No Public API</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Egypt's Ministry of Labour (renamed from Ministry of Manpower in 2023; labour.gov.eg / manpower.gov.eg) is a verified real government ministry that maintains an electronic database for jobseekers and runs online registration campaigns (e.g. for expatriate workers). No public API or developer documentation was discoverable.</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>No Public API</t>
-        </is>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -25881,7 +25873,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
@@ -25988,17 +25980,17 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
@@ -26095,17 +26087,17 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
@@ -26249,47 +26241,47 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
+          <t>Yes - Digital Identity (myGovID). Employers/systems connecting to Workforce Australia for Business must reach at least a 'Standard' identity strength on their Digital Identity and link it to their organisation's ABN via Relationship Authorisation Manager (RAM).</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>General / all industries (national employment service)</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Potentially large</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>General / all industries (national employment service)</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Workforce Australia (workforceaustralia.gov.au, operated by the Department of Employment and Workplace Relations) is the Australian Government's national employment service, having replaced jobactive in July 2022. A 'Connect your system' business portal exists for employers/providers to post and manage job ads, and third-party ATS integrations (e.g. Manatal) link to it, but no public consumer-facing read/search API for retrieving job listings was discoverable. | Access detail: Free (read/search access model unclear)</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t>Potentially large</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Workforce Australia (workforceaustralia.gov.au, operated by the Department of Employment and Workplace Relations) is the Australian Government's national employment service, having replaced jobactive in July 2022. A 'Connect your system' business portal exists for employers/providers to post and manage job ads, and third-party ATS integrations (e.g. Manatal) link to it, but no public consumer-facing read/search API for retrieving job listings was discoverable. | Access detail: Free (read/search access model unclear)</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>Potentially large</t>
-        </is>
-      </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - API is write/management only (create/update/manage employer job ads and their status via OAuth2 RESTful API through the API Developer Portal); no public job-listings read/search endpoint to paginate</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -26685,10 +26677,8 @@
           <t>General / all industries</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+      <c r="H251" t="n">
+        <v>100000</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -26712,7 +26702,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>100,000+ (live jobs)</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -26737,7 +26727,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -27675,7 +27665,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>~209,637 (live listings)</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -27889,7 +27879,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>~1.1 million (110萬, Feb 2026)</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -28210,7 +28200,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>~32,700 (JobsDB HK) / ~32,000 (CTgoodjobs)</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -28745,7 +28735,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>33,600 jobs (live) / 30,000+ job ads</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -28959,7 +28949,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>45,825 jobs (live)</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -29173,7 +29163,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>13,400+ jobs (live)</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -29601,7 +29591,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>68,383 ofertas (live count, Spain, as of July 2026)</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -29795,7 +29785,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>20 calls/cycle limit during 17:00-07:00 access window; service unavailable outside defined hours; two service versions available (legacy /oferta and /v2/oferta with language selection: pl/ru/by/en/ua)</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -29820,7 +29810,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not page/offset-based - full criteria pull via SOAP WebService (POST to /integration/services/oferta or /v2/oferta with a Wojewodztwo/region, Jednostka/office, or Wszystkie/all criterion), returned as a ZIP of JSON files split into batches of max 1,000 offers per file</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -29835,12 +29825,12 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Batch (max 1,000 records/file, criteria-scoped SOAP pull, not a live page/cursor)</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Max 20 service calls per registered Partner per availability cycle during 17:00-07:00 (excess returns 'Przekroczono limit wywolan uslugi'); calls outside MRPiPS-defined access hours return 'Usluga niedostepna'; requires pre-registered Partner name for authorization</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -29922,7 +29912,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>762,827 job offers published in 2025</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -30136,7 +30126,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>4,806 vacancies (live count)</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -30243,7 +30233,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>5,913 ofertas de emprego (live count)</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -32281,7 +32271,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -32296,22 +32286,22 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
@@ -32408,17 +32398,17 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
@@ -32495,7 +32485,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -32510,22 +32500,22 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
@@ -32602,7 +32592,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -32617,12 +32607,12 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -32632,7 +32622,7 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
@@ -32709,7 +32699,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -32724,12 +32714,12 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
@@ -32739,7 +32729,7 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U307" t="inlineStr">
@@ -32816,7 +32806,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -32831,22 +32821,22 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U308" t="inlineStr">
@@ -32923,7 +32913,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -32938,22 +32928,22 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U309" t="inlineStr">
@@ -33152,7 +33142,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -33162,12 +33152,12 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U311" t="inlineStr">
@@ -33886,7 +33876,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page/limit query params: v2 (recommended) - page (default 1) + limit (default 25, max 100); v1 (legacy) - page + limit only, same defaults; iterate ?page=1..N until has_more == false</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -33901,12 +33891,12 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Free, public, no-auth JSON API. 60 requests/minute per IP across /api/v1 and /api/v2 combined; over-limit returns HTTP 429 with Retry-After header; responses cached 60s at edge (Cache-Control: public, max-age=60); jobs refreshed a few times per day</t>
         </is>
       </c>
       <c r="S318" t="inlineStr">
@@ -34095,7 +34085,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>2,000+ hidden remote jobs</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -34334,7 +34324,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S322" t="inlineStr">
@@ -34344,7 +34334,7 @@
       </c>
       <c r="T322" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U322" t="inlineStr">
@@ -34441,7 +34431,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S323" t="inlineStr">
@@ -34451,7 +34441,7 @@
       </c>
       <c r="T323" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U323" t="inlineStr">
@@ -34548,7 +34538,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S324" t="inlineStr">
@@ -34558,7 +34548,7 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U324" t="inlineStr">
@@ -34655,7 +34645,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -34665,7 +34655,7 @@
       </c>
       <c r="T325" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U325" t="inlineStr">
@@ -34762,7 +34752,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S326" t="inlineStr">
@@ -34772,7 +34762,7 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U326" t="inlineStr">
@@ -34869,7 +34859,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S327" t="inlineStr">
@@ -34879,7 +34869,7 @@
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U327" t="inlineStr">
@@ -34976,7 +34966,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -34986,7 +34976,7 @@
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U328" t="inlineStr">
@@ -35083,7 +35073,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S329" t="inlineStr">
@@ -35093,7 +35083,7 @@
       </c>
       <c r="T329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U329" t="inlineStr">
@@ -35190,7 +35180,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S330" t="inlineStr">
@@ -35200,7 +35190,7 @@
       </c>
       <c r="T330" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U330" t="inlineStr">
@@ -35292,12 +35282,12 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -35307,7 +35297,7 @@
       </c>
       <c r="T331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U331" t="inlineStr">
@@ -35399,12 +35389,12 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S332" t="inlineStr">
@@ -35414,7 +35404,7 @@
       </c>
       <c r="T332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U332" t="inlineStr">
@@ -35506,12 +35496,12 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S333" t="inlineStr">
@@ -35521,7 +35511,7 @@
       </c>
       <c r="T333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U333" t="inlineStr">
@@ -35613,12 +35603,12 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S334" t="inlineStr">
@@ -35715,17 +35705,17 @@
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S335" t="inlineStr">
@@ -35735,7 +35725,7 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U335" t="inlineStr">
@@ -35929,7 +35919,7 @@
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
@@ -35939,7 +35929,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S337" t="inlineStr">
@@ -35949,7 +35939,7 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U337" t="inlineStr">
@@ -36036,7 +36026,7 @@
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
@@ -36046,7 +36036,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S338" t="inlineStr">
@@ -36056,7 +36046,7 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U338" t="inlineStr">
@@ -36143,7 +36133,7 @@
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
@@ -36153,7 +36143,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -36163,7 +36153,7 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U339" t="inlineStr">
@@ -36260,7 +36250,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S340" t="inlineStr">
@@ -36270,7 +36260,7 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U340" t="inlineStr">
@@ -36367,7 +36357,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="S341" t="inlineStr">
@@ -36377,7 +36367,7 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="U341" t="inlineStr">
@@ -36469,7 +36459,7 @@
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>N/A - no public read API</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -36531,7 +36521,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>116.8M+</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -36556,12 +36546,12 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>116.8M+ records (general Jobs dataset); LinkedIn Jobs dataset specifically 62.4M+</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Async snapshot model: trigger a collection/filter job, poll status, then GET /datasets/snapshots/{id}/download with batch_size (min 1,000 records/batch) + part (batch number, starting at 1) to page through large snapshot results</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -36576,7 +36566,7 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>part/batch (offset-style batching of a pre-built snapshot)</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -37096,7 +37086,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page-based: page parameter (default 1) on the Jobs Search Results (LinkedIn) endpoint; separate Google Jobs API and Indeed Scraper API products each have their own endpoint-specific pagination</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -37111,7 +37101,7 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -37310,7 +37300,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page-based: page query parameter, up to 25 job listings per page (LinkedIn Job Search endpoint; Indeed Job Search and other endpoints have their own per-endpoint pagination)</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -37325,7 +37315,7 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -37494,7 +37484,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>292M+</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -37519,7 +37509,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>292M+ available jobs</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -37539,7 +37529,7 @@
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>page (default) or cursor (opt-in, mutually exclusive with page-based)</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -37601,7 +37591,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>9.8M+ active jobs (270M+ historical records since 2016)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -37738,7 +37728,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None - async export model: create a search export (Run Search Export), poll for completion, then GET /exports/{id}/leads returns the full array of result rows in a single response (no page/limit params)</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -37753,7 +37743,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None (full result array returned per completed export)</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -37952,7 +37942,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Offset/size via DQL Search API: from (offset, default 0) + size (default 50, max enforced so from+size &lt;= 10,000 for facet queries; size=-1 returns all results)</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -37967,7 +37957,7 @@
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>offset</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -38380,7 +38370,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cursor-based: cursor param + limit (1-200, default 20); next/previous cursors returned in the response's meta.cursors property</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -38395,7 +38385,7 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
